--- a/IT23266032_Assignment 1 - Test cases.xlsx
+++ b/IT23266032_Assignment 1 - Test cases.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\IT232660\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C980BD22-B222-42AE-8383-9ACA1E83F485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D5F1E2C-8B30-4C94-B372-2975957FEC1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="722" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="288">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -46,13 +46,13 @@
     <t>S</t>
   </si>
   <si>
-    <t>oyage aiyata kohomada?</t>
-  </si>
-  <si>
-    <t>ඔයාගේ අයියාට කොහොමද?</t>
-  </si>
-  <si>
-    <t>ඔයාගෙ අයියට කොහොමද?</t>
+    <t>Oya monawada karanne?</t>
+  </si>
+  <si>
+    <t>ඔයා මොනවාද කරන්නේ?</t>
+  </si>
+  <si>
+    <t>ඔයා මොනවද කරන්නේ?</t>
   </si>
   <si>
     <t>FAIL</t>
@@ -61,357 +61,537 @@
     <t>Neg_0002</t>
   </si>
   <si>
+    <t>ඌට එන්න කියන්නේ නෑද?</t>
+  </si>
+  <si>
+    <t>Neg_0003</t>
+  </si>
+  <si>
     <t>M</t>
   </si>
   <si>
-    <t>amme kwdd enna hithن inne? eya kiwwda kohd innava kiyala?</t>
-  </si>
-  <si>
-    <t>අම්මේ කවද්ද එන්න හිතන් ඉන්නේ? එයා කිව්වද කොහේද ඉන්නවා කියලා?</t>
-  </si>
-  <si>
-    <t>අම්මේ කවද්ද එන්න හිතෙන ඉන්නෙ? එයා කිව්වද කුච් ඉන්නව කියල?</t>
-  </si>
-  <si>
-    <t>Neg_0003</t>
-  </si>
-  <si>
-    <t>loku thaththa kivva, wahama enna kiyala</t>
-  </si>
-  <si>
-    <t>ලොකු තාත්තා කිව්වා, වහාම එන්න කියලා.</t>
-  </si>
-  <si>
-    <t>ලොකු තාත්තා කිව්වා, වහාම එන්න කියලා</t>
+    <t>akka kiwwa call krnna epa kiyal.</t>
+  </si>
+  <si>
+    <t>අක්කා කිවුවා call කරන්න එපා කියලා.</t>
+  </si>
+  <si>
+    <t>අක්කා කිව්වා call කරන්න එපා කියලා.</t>
   </si>
   <si>
     <t>Neg_0004</t>
   </si>
   <si>
-    <t>akkata ona mage gawuma, karunakarala mata eka denna.</t>
-  </si>
-  <si>
-    <t>අක්කාට ඕනේ මගේ ගවුම, කරුණාකරලා මට එක දෙන්න.</t>
-  </si>
-  <si>
-    <t>අක්කට ඕන මගේ ගවුම, කරුණාකරලා මට ඒක දෙන්න.</t>
+    <t>karunakarala oya aye mehe enna epa. Man kalinuth kiwuwane oyata</t>
+  </si>
+  <si>
+    <t>කරුණාකරලා ඔයා ආයෙ මෙහෙ එන්න එපා. මන් කලිනුත් කිවුවනේ ඔයාට.</t>
+  </si>
+  <si>
+    <t>කරුණාකරලා ඔයා ආයෙ මෙහේ එන්න එපා. මන් කලිනුත් කිවුවනේ ඔයාට</t>
   </si>
   <si>
     <t>Neg_0005</t>
   </si>
   <si>
-    <t>suba dawasak! Obava gawurawayen piligannava ape mathru bumiyata!</t>
-  </si>
-  <si>
-    <t>සුබ දවසක්! ඔබව ගෞරවයෙන් පිළිගන්නවා අපේ මාතෘ භූමියට!</t>
-  </si>
-  <si>
-    <t>සුබ දවසක්! ඔබව ගවුරවයෙන් පිළිගන්නවා අපේ මාතෘ බූමියට!</t>
+    <t>Jayen jayama wewa!oyata aniwaryen dinanna puluwan.</t>
+  </si>
+  <si>
+    <t>ජයෙන් ජයම වේවා! ඔයාට අනිවාර්යෙන් දිනන්න පුළුවන්.</t>
+  </si>
+  <si>
+    <t>ජයෙන් ජයම වේවා!ඔයාට අනිවාර්යෙන් දිනන්න පුළුවන්.</t>
   </si>
   <si>
     <t>Neg_0006</t>
   </si>
   <si>
-    <t>subha upandinayak wewa nangi!</t>
-  </si>
-  <si>
-    <t>සුභ උපන්දිනයක් වේවා නංගී!</t>
-  </si>
-  <si>
-    <t>සුභ උපන්දිනයක් වේවා නංගි!</t>
+    <t>Ayubowan lamai! Ko anith aya</t>
+  </si>
+  <si>
+    <t>ආයුබෝවන් ළමායි! කෝ අනිත් අය</t>
+  </si>
+  <si>
+    <t>ආයුබෝවන් ළමයි! කෝ අනිත් අය</t>
   </si>
   <si>
     <t>Neg_0007</t>
   </si>
   <si>
-    <t>oyata puluwannam eyata eka gana kiyanna.</t>
-  </si>
-  <si>
-    <t>ඔයාට පුලුවන්නම් එයාට එක ගැන කියන්න.</t>
-  </si>
-  <si>
-    <t>ඔයාට පුලුවන්නම් එයාට එක ගාන කියන්න.</t>
+    <t>Ane nangi mata eka genalla denawada?</t>
+  </si>
+  <si>
+    <t>අනේ නංගී මට ඒක ගෙනල්ල දෙනවද?</t>
+  </si>
+  <si>
+    <t>අනේ නංගි මට ඒක ගෙනල්ල දෙනවද?</t>
   </si>
   <si>
     <t>Neg_0008</t>
   </si>
   <si>
-    <t>krnakarla mata pddak udaw kranna, mge assignment eka finish krnn one nxt wk tnkn.</t>
-  </si>
-  <si>
-    <t>කරුණාකරලා මට පොඩ්ඩක් උදව් කරන්න, මගේ assignment එක finish කරන්න ඕනේ next week තෙනකන්.</t>
-  </si>
-  <si>
-    <t>කරන්නකරලා මට පද්දක් උදව් කරන්න, මගේ assignment එක finish කරන්න ඕනේ nxt week තෑන්කන්.</t>
+    <t>oya yana gaman ammata meka deegena yanawada?</t>
+  </si>
+  <si>
+    <t>ඔයා යන ගමන් අම්මට මේක දීගෙන යනවද?</t>
   </si>
   <si>
     <t>Neg_0009</t>
   </si>
   <si>
-    <t>hari, mama eka hoyala balnnam.</t>
-  </si>
-  <si>
-    <t>හරි, මම එක හොයලා බලන්නම්.</t>
-  </si>
-  <si>
-    <t>හරි, මම ඒක හොයලා බලන්නම්.</t>
+    <t>Ane oka mokakda, man liyala dannam.</t>
+  </si>
+  <si>
+    <t>අනේ ඕක මොකක්ද, මං ලියල දෙන්නම්.</t>
+  </si>
+  <si>
+    <t>අනේ ඕක මොකක්ද, මං ලියල දාන්නම්.</t>
   </si>
   <si>
     <t>Neg_0010</t>
   </si>
   <si>
+    <t>Na na ,eka kohethma wenna widiyak nane.</t>
+  </si>
+  <si>
+    <t>නැ නැ ,ඒක කොහෙත්ම වෙන්න විදියක් නෑනේ.</t>
+  </si>
+  <si>
+    <t>නෑ නෑ ,ඒක කොහෙත්ම වෙන්න විදියක් නෑනේ.</t>
+  </si>
+  <si>
+    <t>Neg_0011</t>
+  </si>
+  <si>
+    <t>Adanam traffic eke idala idala epa una.</t>
+  </si>
+  <si>
+    <t>අදනම් traffic එකේ ඉඳලා ඉඳලා එපා වුණා.</t>
+  </si>
+  <si>
+    <t>Neg_0012</t>
+  </si>
+  <si>
+    <t>Epa epa, oya yanna oni na.</t>
+  </si>
+  <si>
+    <t>එපා එපා, ඔයා යන්න ඕනි නෑ.</t>
+  </si>
+  <si>
+    <t>එපා එපා, ඔයා යන්න ඕනේ නෑ.</t>
+  </si>
+  <si>
+    <t>Neg_0013</t>
+  </si>
+  <si>
+    <t>Mama kanna yanaw. oya enawada?</t>
+  </si>
+  <si>
+    <t>මම කන්න යනවා... ඔයා එනවාද?</t>
+  </si>
+  <si>
+    <t>Neg_0014</t>
+  </si>
+  <si>
+    <t>Ayyo! Eyata thuwala welada?</t>
+  </si>
+  <si>
+    <t>අයියො! එයාට තුවාල වෙලාද?</t>
+  </si>
+  <si>
+    <t>Neg_0015</t>
+  </si>
+  <si>
     <t>ane. Ehemada siyee oyata godak pin.</t>
   </si>
   <si>
     <t>අනේ. එහෙමද සියේ ඔයාට ගොඩක් පිං.</t>
   </si>
   <si>
+    <t>අයියෝ! එයාට තුවාල වෙලාද?</t>
+  </si>
+  <si>
+    <t>Neg_0016</t>
+  </si>
+  <si>
+    <t>Oya dath maddnam ikmanata yan.Parkku wei.</t>
+  </si>
+  <si>
+    <t>ඔයා දත් මැද්දනම් ඉක්මනට යමු.පරක්කු වෙයි.</t>
+  </si>
+  <si>
     <t>අනේ. එහෙමද සීයා ඔයාට ගොඩක් පින්.</t>
   </si>
   <si>
-    <t>Neg_0011</t>
-  </si>
-  <si>
-    <t>ow ow, eka mama ada dawasa athulatha iwra karnnam.</t>
-  </si>
-  <si>
-    <t>ඔව් ඔව්, එක මම අද දවස ඇතුලාට ඉවර කරන්නම්.</t>
-  </si>
-  <si>
-    <t>ඔව් ඔව්, ඒක මම අද දවස ඇතුලත ඉවර කරන්නම්.</t>
-  </si>
-  <si>
-    <t>Neg_0012</t>
-  </si>
-  <si>
-    <t>eka eka karala hadanna, ekata karanna epa.</t>
-  </si>
-  <si>
-    <t>එක එක කරලා හදන්න, එකට කරන්න එපා.</t>
-  </si>
-  <si>
-    <t>එක එක කරලා හදන්න, ඒකට කරන්න එපා.</t>
-  </si>
-  <si>
-    <t>Neg_0013</t>
-  </si>
-  <si>
-    <t>mata therenne nehe... oya mokada kiwwe?</t>
-  </si>
-  <si>
-    <t>මට තේරෙන්නේ නෑ... ඔයා මොකද කිව්වේ?</t>
-  </si>
-  <si>
-    <t>මට තේරෙන්නෙ නැහැ... ඔයා මොකද කිව්වෙ?</t>
-  </si>
-  <si>
-    <t>Neg_0014</t>
-  </si>
-  <si>
-    <t>ane! koheda oya giye, kiyanna.</t>
-  </si>
-  <si>
-    <t>අනේ! කොහේද ඔයා ගියේ, කියන්න.</t>
-  </si>
-  <si>
-    <t>අනේ! කොහෙද ඔයා ගියේ, කියන්න.</t>
-  </si>
-  <si>
-    <t>Neg_0015</t>
-  </si>
-  <si>
-    <t>mama mage nonata adareyi.</t>
-  </si>
-  <si>
-    <t>මම මගේ නෝනාට ආදරෙයි.</t>
-  </si>
-  <si>
-    <t>මම මගේ නෝනට ආදරෙයි.</t>
-  </si>
-  <si>
-    <t>Neg_0016</t>
-  </si>
-  <si>
-    <t>api oyata psse katha krannam.</t>
-  </si>
-  <si>
-    <t>අපි ඔයාට පස්සේ කතා කරන්නම්.</t>
-  </si>
-  <si>
-    <t>PASS</t>
-  </si>
-  <si>
     <t>Neg_0017</t>
   </si>
   <si>
-    <t>psse aluth geyk hdagnn, interior design ekk krnn loan ekk apply krla blmu.</t>
-  </si>
-  <si>
-    <t>පස්සේ අළුත් ගෙයක් හදාගන්න, interior design එකක් කරන්න loan එකක් apply කරලා බලමු.</t>
-  </si>
-  <si>
-    <t>පස්සේ අලුත් ගෙයක් හදාගන්න, interior design එකක් කරන්න loan එකක් apply කරලා බලමු.</t>
+    <t xml:space="preserve">Mata asaneepai wage nisa heta office enna wenne na.  </t>
+  </si>
+  <si>
+    <t>මට අසනීපයි වගේ නිසා හෙට office එන්න වෙන්නේ නැ.</t>
+  </si>
+  <si>
+    <t>ඔය දත් මද්දනම් ඉක්මනට යමු.පර්ක්කු වෙයි.</t>
   </si>
   <si>
     <t>Neg_0018</t>
   </si>
   <si>
-    <t>ai anee aiyee, oyta akkage birthday ekawath mthaka nadda.</t>
-  </si>
-  <si>
-    <t>අයි අනේ අයියේ, ඔයාට අක්කාගේ birthday එකවත් මතක නැද්ද.</t>
-  </si>
-  <si>
-    <t>ඇයි අනේ අයියේ, ඔයාට අක්කගේ birthday එකවත් මතක නැද්ද.</t>
+    <t>Man gaththe oppo wala apu aluth phone eka.</t>
+  </si>
+  <si>
+    <t>මන් ගත්තේ oppo වල ආපු අලුත් phone එක.</t>
+  </si>
+  <si>
+    <t>මට අසනීපයි වගේ නිසා හෙට office එන්න වෙන්නේ නෑ.</t>
   </si>
   <si>
     <t>Neg_0019</t>
   </si>
   <si>
-    <t>ai anee aiyee, oyta akkage annivasary ekawath mthaka nadda.</t>
-  </si>
-  <si>
-    <t>අයි අනේ අයියේ, ඔයාට අක්කාගේ anniversary එකවත් මතක නැද්ද.</t>
-  </si>
-  <si>
-    <t>ඇයි අනේ අයියේ, ඔයාට අක්කගේ අනිවාසර්ය් එකවත් මතක නැද්ද.</t>
+    <t>See you tomorrow machan.</t>
+  </si>
+  <si>
+    <t>See you tomorrow මචන්.</t>
   </si>
   <si>
     <t>Neg_0020</t>
   </si>
   <si>
-    <t>mama ada lunch ekata eliyata yannada?</t>
-  </si>
-  <si>
-    <t>මම අද lunch එකට එළියට යන්නද?</t>
-  </si>
-  <si>
-    <t>මම අද lunch එකට එලියට යන්නද?</t>
+    <t>api dubai shopping karnna ymuda?</t>
+  </si>
+  <si>
+    <t>අපි dubai shopping කරන්න යමුද?</t>
+  </si>
+  <si>
+    <t>සී යූ tomorrow මචන්.</t>
   </si>
   <si>
     <t>Neg_0021</t>
   </si>
   <si>
-    <t>api aluthen dapu restaurant ekata ymuda ada hawata.</t>
-  </si>
-  <si>
-    <t>අපි අලුතෙන් දාපු restaurant එකට යමුද අද හවාට.</t>
-  </si>
-  <si>
-    <t>අපි අලුතෙන් දාපු restaurant එකට යමුද අද හාවට.</t>
+    <t>ehata wifi signal nalu.</t>
+  </si>
+  <si>
+    <t>එහාට wifi signal නෑලු.</t>
+  </si>
+  <si>
+    <t>අපි ඩුබායි shopping කරන්න යමුද?</t>
   </si>
   <si>
     <t>Neg_0022</t>
   </si>
   <si>
-    <t>eya kwwa no problem, api handle krnnm kiyala. dnt wrry, team eka together manage krla solve krnnm.</t>
-  </si>
-  <si>
-    <t>එයා කිව්වා no problem, අපි handle කරන්නම් කියලා. don't worry, team එක together manage කරලා solve කරන්නම්.</t>
-  </si>
-  <si>
-    <t>එයා කිව්වා no problem, අපි handle කරන්නම් කියලා. දැනට වැරදියි, team එක together manage කරලා solve කරන්නම්.</t>
+    <t>Mata heta ena driver ge number eka denna?</t>
+  </si>
+  <si>
+    <t>මට හෙට එන driver ගෙ number එක දෙන්න?</t>
+  </si>
+  <si>
+    <t>එහාට wifi signal නළු.</t>
   </si>
   <si>
     <t>Neg_0023</t>
   </si>
   <si>
-    <t>eyala dn otw, gonna b thr sn.</t>
-  </si>
-  <si>
-    <t>එයාලා දැන් on the way, gonna be there soon.</t>
-  </si>
-  <si>
-    <t>එයාලා දැන් ඔටුවා, ගොන්න බෑ ත් සීන්.</t>
+    <t>Api aniddata yanna Pick me ekak damu.</t>
+  </si>
+  <si>
+    <t>අපි අනිද්දාට යන්න Pick me එකක් දාමු.</t>
+  </si>
+  <si>
+    <t>අපි අනිද්දාට යන්න Pick මේ එකක් දාමු.</t>
   </si>
   <si>
     <t>Neg_0024</t>
   </si>
   <si>
-    <t>ehata wifi signal nalu.</t>
-  </si>
-  <si>
-    <t>එහාට wifi signal නෑළු.</t>
-  </si>
-  <si>
-    <t>එහාට wifi signal නළු.</t>
+    <t xml:space="preserve">Oya facebook use karala oyage time eka nasthi karanawa. </t>
+  </si>
+  <si>
+    <t>ඔය Facebook use කරලා ඔයාගේ time එක නාස්ති කරනවා.</t>
+  </si>
+  <si>
+    <t>ඔයා Facebook use කරලා ඔයාගේ time එක නාස්ති කරනවා.</t>
   </si>
   <si>
     <t>Neg_0025</t>
   </si>
   <si>
-    <t>oya screenshot eka send karannako.</t>
-  </si>
-  <si>
-    <t>ඔය screenshot එක send කරන්නකෝ.</t>
-  </si>
-  <si>
-    <t>ඔයා screenshot එක send කරන්නකෝ.</t>
+    <t>Heta enakota ID eka aniwaryen aran enna one.</t>
+  </si>
+  <si>
+    <t>හෙට එනකොට ID එක අනිවාර්යෙන් අරන් එන්න ඕනේ.</t>
   </si>
   <si>
     <t>Neg_0026</t>
   </si>
   <si>
-    <t>mama Instagram eke post eka dala thiyanawa.</t>
-  </si>
-  <si>
-    <t>මම Instagram එකේ post එක දාලා තියනවා.</t>
-  </si>
-  <si>
-    <t>මම Instagram එකේ post එක දාලා තියෙනවා.</t>
+    <t xml:space="preserve">Karunakara EOD eka iwra karanna.. </t>
+  </si>
+  <si>
+    <t>කරුණාකර EOD ඒක ඉවර කරන්න..</t>
   </si>
   <si>
     <t>Neg_0027</t>
   </si>
   <si>
-    <t>oya YouTube eke video eka baluwada?</t>
-  </si>
-  <si>
-    <t>ඔය YouTube එකේ video එක බැලුවද?</t>
-  </si>
-  <si>
-    <t>ඔයා YouTube එකේ video එක බැලුවද?</t>
+    <t>Ayya uni ekata giyane.</t>
+  </si>
+  <si>
+    <t>අයියා uni එකට ගියානේ.</t>
+  </si>
+  <si>
+    <t>අයියා උනි එකට ගියානේ.</t>
   </si>
   <si>
     <t>Neg_0028</t>
   </si>
   <si>
-    <t>Principle keewa ASAP ground ekata enna kiyala.</t>
-  </si>
-  <si>
-    <t>Principle කිවා ASAP ground එකට එන්න කියලා.</t>
-  </si>
-  <si>
-    <t>Principle කීවා ASAP ground එකට එන්න කියලා.</t>
-  </si>
-  <si>
     <t>Neg_0029</t>
   </si>
   <si>
-    <t>hamogema NIC check karala athualata ganne.</t>
-  </si>
-  <si>
-    <t>හාමෝගේම NIC check කරලා ඇතුලාට ගන්නේ.</t>
-  </si>
-  <si>
-    <t>හැමෝගෙම NIC චෙක් කරලා අතුඅලට ගන්නේ.</t>
+    <t>api Kandy side trip ekk yanwda nxt wk? hodai ne machan</t>
+  </si>
+  <si>
+    <t>අපි Kandy side trip එකක් යනවද next week? හොඳයි නේ මචන්</t>
   </si>
   <si>
     <t>Neg_0030</t>
   </si>
   <si>
-    <t>mama ada uni eka giyane bus eken.</t>
-  </si>
-  <si>
-    <t>මම අද uni එකට ගියේ bus එකෙන්.</t>
-  </si>
-  <si>
-    <t>මම අද උනි එක ගියානේ බස් එකෙන්.</t>
+    <t>L</t>
+  </si>
+  <si>
+    <t>Api dan trip ekak plan karanawa next month walata yanna. mama hithanne Riverston walata yanna hari hondai kiyala mokada ehema place ekak relax wenna puluwan nisa. oyata puluwannam hotel ekak book karanna balanna. mama dan internet eken reviews tika balala thiyenawa but decision ekak ganna ba.</t>
+  </si>
+  <si>
+    <t>අපි Kandy side trip එකක් යනවද nxt එකක්? හොදයි නේ මචං</t>
   </si>
   <si>
     <t>Neg_0031</t>
   </si>
   <si>
+    <t>Wasare dakshathama sisuwiya une  Hashini.</t>
+  </si>
+  <si>
+    <t>වසරේ දක්ෂතම සිසුවිය උනේ Hashini.</t>
+  </si>
+  <si>
+    <t>Neg_0032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heta man wenuwata Viweka ennam kiwuwa.  </t>
+  </si>
+  <si>
+    <t>හෙට මං වෙනුවට විවේකා එන්නම් කිවුවා.</t>
+  </si>
+  <si>
+    <t>වසරේ දක්ෂතම සිසුවිය උනේ හෂිනි.</t>
+  </si>
+  <si>
+    <t>Neg_0033</t>
+  </si>
+  <si>
+    <t>E brand ekta ISO 4032 th thiynawa.</t>
+  </si>
+  <si>
+    <t>ඒ brand එකට ISO 4032 ත් තියෙනවා.</t>
+  </si>
+  <si>
+    <t>හෙට මං වෙනුවට විවේක එන්නම් කිවුවා.</t>
+  </si>
+  <si>
+    <t>Neg_0034</t>
+  </si>
+  <si>
+    <t>Grade 8 lamai harima hodai.</t>
+  </si>
+  <si>
+    <t>Grade 8 ළමයි හරිම හොඳයි.</t>
+  </si>
+  <si>
+    <t>ඒ brand එකට ISO 4032 තියනවා.</t>
+  </si>
+  <si>
+    <t>Neg_0035</t>
+  </si>
+  <si>
+    <t>Ape akka magen Rs.3000 k nayata gaththa.</t>
+  </si>
+  <si>
+    <t>අපේ අක්කා මගෙන් Rs.3000 ක් ණයට ගත්තා.</t>
+  </si>
+  <si>
+    <t>ග්රාදේ 8 ළමයි හරිම හොඳයි.</t>
+  </si>
+  <si>
+    <t>Neg_0036</t>
+  </si>
+  <si>
+    <t>E  manussaya USD 50k horakam karala.</t>
+  </si>
+  <si>
+    <t>ඒ මනුස්සයා USD 50k හොරකම් කරලා.</t>
+  </si>
+  <si>
+    <t>අපේ අක්ක මගෙන් Rs.3000 ක් ණයට ගත්තා.</t>
+  </si>
+  <si>
+    <t>Neg_0037</t>
+  </si>
+  <si>
+    <t>5am t enne ai?</t>
+  </si>
+  <si>
+    <t>5am ට එන්නේ ඇයි?</t>
+  </si>
+  <si>
+    <t>ඒ මනුස්සයා USD 50ක් හොරකම් කරලා.</t>
+  </si>
+  <si>
+    <t>Neg_0038</t>
+  </si>
+  <si>
+    <t>Eyala ehen enna 8am pahu wei.</t>
+  </si>
+  <si>
+    <t>එයාලා එහෙන් එන්න 8am පහු වෙයි</t>
+  </si>
+  <si>
+    <t>5ට එන්නේ ඇයි?</t>
+  </si>
+  <si>
+    <t>Neg_0039</t>
+  </si>
+  <si>
+    <t>එයාලා එහෙන් එන්න 8ම් පහු වෙයි.</t>
+  </si>
+  <si>
+    <t>Neg_0040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eyalage ilnga anniversary eka March 25 </t>
+  </si>
+  <si>
+    <t>එයාලගේ ඊලග anniversary එක March 25</t>
+  </si>
+  <si>
+    <t>Neg_0041</t>
+  </si>
+  <si>
+    <t>gedara floor eka square feet 1200k wage.</t>
+  </si>
+  <si>
+    <t>එයාලගේ ඊළඟ anniversary එක මාර්තු 25</t>
+  </si>
+  <si>
+    <t>Neg_0042</t>
+  </si>
+  <si>
+    <t>Wahanayak nathnam 2km withara pain yanna wenwa</t>
+  </si>
+  <si>
+    <t>වාහනයක් නැත්නම් 2km විතර පයින් යන්න වෙනවා</t>
+  </si>
+  <si>
+    <t>ගෙදර floor එක square feet 1200ක් වගේ.</t>
+  </si>
+  <si>
+    <t>Neg_0043</t>
+  </si>
+  <si>
+    <t>Adoh, cupiri wadak ekanam.</t>
+  </si>
+  <si>
+    <t>අඩෝ, සුපිරි වැඩක් ඒකනම්.</t>
+  </si>
+  <si>
+    <t>වාහනයක් නැත්නම් 2km විතර පෑන් යන්න වෙනවා</t>
+  </si>
+  <si>
+    <t>Neg_0044</t>
+  </si>
+  <si>
+    <t>Patta ne ban</t>
+  </si>
+  <si>
+    <t>පට්ට නේ බං</t>
+  </si>
+  <si>
+    <t>අඩෝ, කූපිරි වැඩක් ඒකනම්.</t>
+  </si>
+  <si>
+    <t>Neg_0045</t>
+  </si>
+  <si>
+    <t>https:/www.youtube.com/watch? Me link eke videos thiyanwa.</t>
+  </si>
+  <si>
+    <t>https:/www.youtube.com/watch? මේ link එකේ videos තියෙනවා.</t>
+  </si>
+  <si>
+    <t>පට්ට නෑ බං</t>
+  </si>
+  <si>
+    <t>Neg_0046</t>
+  </si>
+  <si>
+    <t>Magee email eka anudi@gmail.com kiyala man change kala.</t>
+  </si>
+  <si>
+    <t>මගේ email එක anudi@gmail.com කියලා මන් change කළා.</t>
+  </si>
+  <si>
+    <t>https:/www.යූටූබ්.com/watch? මේ link එකේ videos තියෙනවා.</t>
+  </si>
+  <si>
+    <t>Neg_0047</t>
+  </si>
+  <si>
+    <t>Mara wadak neh uta wela thiyenne 😅</t>
+  </si>
+  <si>
+    <t>මාර වැඩක් නේ  ඌට වෙලා තියෙන්නේ 😅</t>
+  </si>
+  <si>
+    <t>මගේ email එක අනුදි@gmail.කොම් කියලා මං change කළා.</t>
+  </si>
+  <si>
+    <t>Neg_0048</t>
+  </si>
+  <si>
+    <t>Eya ehema innawa mata balan inn amaruiii  😔</t>
+  </si>
+  <si>
+    <t>එයා එහෙම ඉන්නවා මට බලන් ඉන්න අමාරුයි 😔</t>
+  </si>
+  <si>
+    <t>මාර වැඩක් නෙහ් ඌට වෙලා තියෙන්නේ 😅</t>
+  </si>
+  <si>
+    <t>Neg_0049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oyata puluwannam me document eka print karala office ekata genna </t>
+  </si>
+  <si>
+    <t>ඔයාට පුළුවන්නම් මේ document එක print කරලා office එකට ගෙනෙන්න</t>
+  </si>
+  <si>
+    <t>එයා එහෙම ඉන්නවා මට බලන් ඉන්න අමාරුයි</t>
+  </si>
+  <si>
+    <t>Neg_0050</t>
+  </si>
+  <si>
+    <t>ඔයාට පුලුවන්නම් මේ document එක print කරලා office එකට ගේන්න</t>
+  </si>
+  <si>
+    <t>කරුණාකර EOD එක ඉවර කරන්න..</t>
+  </si>
+  <si>
     <t>oyalage lab eka wenas karala.</t>
   </si>
   <si>
@@ -421,79 +601,46 @@
     <t>ඔයාලගේ ලබ් එක වෙනස් කරලා.</t>
   </si>
   <si>
-    <t>Neg_0032</t>
-  </si>
-  <si>
-    <t>api Kndy side trip ekk yanwda nxt wk? hodai ne machan</t>
-  </si>
-  <si>
-    <t>අපි Kandy side trip එකක් යනවද next week? හොඳයි නේ මචන්</t>
-  </si>
-  <si>
-    <t>අපි Kndy side trip එකක් යනවද nxt week? හොදයි නේ මචං</t>
-  </si>
-  <si>
-    <t>Neg_0033</t>
-  </si>
-  <si>
-    <t>api dubai shopping karnna ymuda?</t>
-  </si>
-  <si>
-    <t>අපි dubai shopping කරන්න යමුද?</t>
-  </si>
-  <si>
-    <t>අපි ඩුබායි shopping කරන්න යමුද?</t>
-  </si>
-  <si>
-    <t>Neg_0034</t>
-  </si>
-  <si>
-    <t>Kamal aiyee, oya ada enawada?</t>
-  </si>
-  <si>
-    <t>Kamal අයියේ, ඔයා අද එනවද?</t>
-  </si>
-  <si>
-    <t>කමල් අයියේ, ඔයා අද එනවද?</t>
-  </si>
-  <si>
-    <t>Neg_0035</t>
-  </si>
-  <si>
-    <t>eye match ekedi Thisara perera hodata gahuwa.</t>
-  </si>
-  <si>
-    <t>ඒ match එකේදී Thisara perera හොඳට ගැහුවා.</t>
-  </si>
-  <si>
-    <t>ඊයේ match එකේදී Thisara පෙරේරා හොදට ගැහුවා.</t>
-  </si>
-  <si>
-    <t>Neg_0036</t>
-  </si>
-  <si>
-    <t>salary eka 50k withara thiyenawa.</t>
-  </si>
-  <si>
-    <t>salary එක 50k විතර තියෙනවා.</t>
-  </si>
-  <si>
-    <t>salary එක 50ක් විතර තියෙනවා.</t>
-  </si>
-  <si>
-    <t>Neg_0037</t>
-  </si>
-  <si>
-    <t>wedding eke 2nd date eka gedara thiyamu.</t>
-  </si>
-  <si>
-    <t>wedding එකේ second date එක ගෙදර තියමු.</t>
-  </si>
-  <si>
-    <t>wedding එකේ 2nd date එක ගෙදර තියමු.</t>
-  </si>
-  <si>
-    <t>Neg_0038</t>
+    <t>ඔයා යන ගමන් අම්මා ට මේක දීගෙන යනවද?</t>
+  </si>
+  <si>
+    <t>ඌට එන්න කියන්නේ නැද්ද?</t>
+  </si>
+  <si>
+    <t>Uta enna kiyanne nadda?</t>
+  </si>
+  <si>
+    <t>අදනම් traffic එකෙ ඉඳලා ඉඳලා එපා වුණා.</t>
+  </si>
+  <si>
+    <t>මම කන්න යනවා... ඔයා එනවද?</t>
+  </si>
+  <si>
+    <t>හෙට එනකොට ID ඒක අනිවාර්යෙන් අරන් එන්න ඕනේ.</t>
+  </si>
+  <si>
+    <t>අපි දැන් trip එකක් plan කරනවා next month වලට යන්න. මම හිතන්නේ රිවර්ස්ටෝන් වලට යන්න හරි හොඳයි කියලා මොකද එහෙම place එකක් relax වෙන්න පුළුවන් නිසා. ඔයාට පුලුවන්නම් හොටෙල් එකක් book කරන්න බලන්න. මම දැන් internet එකෙන් reviews ටික බලලා තියෙනවා but decision එකක් ගන්න බෑ.</t>
+  </si>
+  <si>
+    <t>අපි දැන් trip එකක් plan කරනවා next month වලට යන්න. මම හිතන්නේ Riverston වලට යන එක හොඳයි කියලා මොකද එහෙම place එකක් relax වෙන්න පුළුවන් නිසා. ඔයාට පුලුවන්නම් හොටෙල් එකක් book කරන්න බලන්න. මම දැන් internet එකෙන් reviews ටික බලලා තියෙනවා but decision එකක් ගන්න බෑ.</t>
+  </si>
+  <si>
+    <t>ගෙදර floor එක square feet 1200k වගේ</t>
+  </si>
+  <si>
+    <t>මට හෙට එන driver ගේ number එක දෙන්න?</t>
+  </si>
+  <si>
+    <t>මන් ගත්තේ ඔප්පෝ වල ආපු අලුත් phone එක.</t>
+  </si>
+  <si>
+    <t>Ayith mamala 2026-6-10 Jaffna yanwa</t>
+  </si>
+  <si>
+    <t>ආයිත් මමලා 2026-6-10 Jaffna යනවා</t>
+  </si>
+  <si>
+    <t>ආයිත් මාමලා 2026-6-10 Jaffna යනවා</t>
   </si>
   <si>
     <t>e jeans eka Rs. 3500 ta gatta.</t>
@@ -505,454 +652,238 @@
     <t>ඒ ජින්ස් එක Rs. 3500 ට ගත්තා.</t>
   </si>
   <si>
-    <t>Neg_0039</t>
-  </si>
-  <si>
-    <t>USD 500 kiyanne rupiyal walin kochcharada?</t>
-  </si>
-  <si>
-    <t>USD 500 කියන්නේ RS වලින් කොච්චරද?</t>
-  </si>
-  <si>
-    <t>USD 500 කියන්නේ රුපියල් වලින් කොච්චරද?</t>
-  </si>
-  <si>
-    <t>Neg_0040</t>
-  </si>
-  <si>
-    <t>class eka 8:30AM ta tiyenawa.</t>
-  </si>
-  <si>
-    <t>class එක 8:30AM ට තියෙනවා.</t>
-  </si>
-  <si>
-    <t>class එක 8:30ට තියෙනවා.</t>
-  </si>
-  <si>
-    <t>Neg_0041</t>
-  </si>
-  <si>
-    <t>api 8am walata school yamu.</t>
-  </si>
-  <si>
-    <t>අපි 8am වලට school යමු!</t>
-  </si>
-  <si>
-    <t>අපි 8ම් වලට school යමු.</t>
-  </si>
-  <si>
-    <t>Neg_0042</t>
-  </si>
-  <si>
-    <t>birthday eka March 22 dha?</t>
-  </si>
-  <si>
-    <t>birthday එක March twenty two ද?</t>
-  </si>
-  <si>
-    <t>birthday එක March 22 ද?</t>
-  </si>
-  <si>
-    <t>Neg_0043</t>
-  </si>
-  <si>
-    <t>deadline eka 2026-04-30 t tiyenawa.</t>
-  </si>
-  <si>
-    <t>deadline එක 2026-04-30 ට තියෙනවා.</t>
-  </si>
-  <si>
-    <t>deadline එක 2026-04-30 ටී තියෙනවා.</t>
-  </si>
-  <si>
-    <t>Neg_0044</t>
-  </si>
-  <si>
-    <t>eh gas bottle eka kg 12kg</t>
-  </si>
-  <si>
-    <t>ඒ gas bottle එක කිලෝග්‍රෑම් 12ක්.</t>
-  </si>
-  <si>
-    <t>ඒ gas bottle එක kg 12kg</t>
-  </si>
-  <si>
-    <t>Neg_0045</t>
-  </si>
-  <si>
-    <t>gedara inda School eka km 5k withara.</t>
-  </si>
-  <si>
-    <t>ගෙදර ඉඳලා School එක km 5ක් විතර.</t>
-  </si>
-  <si>
-    <t>ගෙදර ඉඳ ඉස්කෝලේ එක km 5ක් විතර.</t>
-  </si>
-  <si>
-    <t>Neg_0046</t>
-  </si>
-  <si>
-    <t>adoo, elakiri bro, uba hodata wade kara.</t>
-  </si>
-  <si>
-    <t>අඩෝ, එළකිරි bro, උඹ හොඳට වැඩේ කරා.</t>
-  </si>
-  <si>
-    <t>අඩෝ, එළකිරි bro, උඹ හොදට වඩේ කරා.</t>
-  </si>
-  <si>
-    <t>Neg_0047</t>
-  </si>
-  <si>
-    <t>ube wada elakiri kiyala hamoma dannava bng.</t>
-  </si>
-  <si>
-    <t>උඹේ වැඩ එළකිරි කියලා හාමෝම දන්නවා bng.</t>
-  </si>
-  <si>
-    <t>උබේ වැඩ එළකිරි කියලා හැමෝම දන්නවා බන්ග්.</t>
-  </si>
-  <si>
-    <t>Neg_0048</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> aiye oya ada online da meeting eka iwra unata passe @saman?</t>
-  </si>
-  <si>
-    <t>අයියේ ඔයා අද online ද meeting එක ඉවර උනාට පස්සේ @saman?</t>
-  </si>
-  <si>
-    <t>අයියේ ඔයා අද online ද meeting එක ඉවර වුණාට පස්සේ @සමන්?</t>
-  </si>
-  <si>
-    <t>Neg_0049</t>
-  </si>
-  <si>
-    <t>subha uppandawasak wewa 🎉 machan!</t>
-  </si>
-  <si>
-    <t>සුභ උප්පන්දවසක් වේවා 🤣 මචං!</t>
-  </si>
-  <si>
-    <t>COLLECTED</t>
-  </si>
-  <si>
-    <t>Neg_0050</t>
-  </si>
-  <si>
-    <t>mama Rs. 1500 dala Instagram eke ad ekak dunnaa. eheth godak like nehe, comment ekak wath nehe. mama hithanne Instagram algorithm eka mage post suppress karala thiyenna. eka nisa mama target audience eka change karala, caption eka wath update karala, hash tags wath add karala balaawa. eheth still Rs. 1500 wasthu wuna wage thiyenne nehe.</t>
-  </si>
-  <si>
-    <t>මම Rs. 1500 දාලා Instagram එකේ ad එකක් දුන්නා. ඒත් ගොඩක් like නෑ…</t>
-  </si>
-  <si>
-    <t>මම Rs. 1500 දාලා Instagram එකේ ad එකක් දුන්නා. එහෙත් ගොඩක් ලයික් නැහැ, comment එකක් වත් නැහැ. මම හිතන්නේ Instagram algorithm එක මගේ post suppress කරලා තියෙන්න. ඒක නිසා මම target audience එක change කරලා, caption එක වත් update කරලා, hash tags වත් add කරලා බලවා. එහෙත් still Rs. 1500 වස්තු වුනා වගේ තියෙන්නෙ නැහැ.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Singlish input types covered </t>
-  </si>
-  <si>
-    <t>Evidence or rationale for the input type covered</t>
-  </si>
-  <si>
-    <t>Simple phonetic typing</t>
-  </si>
-  <si>
-    <t>Mixed Sinhala-English words</t>
-  </si>
-  <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t>"oyage", "kohomada" typed using Sinhala sounds in English</t>
-  </si>
-  <si>
-    <t>Formal sinhala in english</t>
-  </si>
-  <si>
-    <t>"loku thaththa kivva" reflects formal spoken Sinhala typed in English</t>
-  </si>
-  <si>
-    <t>Polite request structure</t>
-  </si>
-  <si>
-    <t>"karunakarala" indicates formal/polite Sinhala expression</t>
-  </si>
-  <si>
-    <t>Frormal greeting sentence</t>
-  </si>
-  <si>
-    <t>Full formal Sinhala sentence typed in Singlish</t>
-  </si>
-  <si>
-    <t>celebration phrase</t>
-  </si>
-  <si>
-    <t>"subha upandinayak" commonly used greeting in phonetic form</t>
-  </si>
-  <si>
-    <t>Instructional sentence</t>
-  </si>
-  <si>
-    <t>"kiyanna" indicates giving instructions</t>
-  </si>
-  <si>
-    <t>Abbreviations + mixed language</t>
-  </si>
-  <si>
-    <t>"krnakarla", "pddak", "nxt wk" show heavy shortening</t>
-  </si>
-  <si>
-    <t>Casual conversational Singlish</t>
-  </si>
-  <si>
-    <t>Simple everyday spoken Sinhala typed in English</t>
-  </si>
-  <si>
-    <t>emotional and respectful tone</t>
-  </si>
-  <si>
-    <t>"ane", "siyee" reflect emotion and respect</t>
-  </si>
-  <si>
-    <t>Repetition for emphasis</t>
-  </si>
-  <si>
-    <t>"ow ow" used to emphasize agreement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Repeated structure </t>
-  </si>
-  <si>
-    <t>"eka eka" shows duplication pattern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">informal question </t>
-  </si>
-  <si>
-    <t>"..." and casual questioning</t>
-  </si>
-  <si>
-    <t>Exclamatory srntence</t>
-  </si>
-  <si>
-    <t>"ane!" expresses emotion</t>
-  </si>
-  <si>
-    <t>Personal/emotional expression</t>
-  </si>
-  <si>
-    <t>"adareyi" expresses affection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shorted words </t>
-  </si>
-  <si>
-    <t>"psse" instead of "passe"</t>
-  </si>
-  <si>
-    <t>heavy abbreviation and hybrid words</t>
-  </si>
-  <si>
-    <t>hdagnn", "ekk", "krnn" shortened forms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">slang expression </t>
-  </si>
-  <si>
-    <t>"ai anee aiyee" informal emotional speech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Misspelling </t>
-  </si>
-  <si>
-    <t>"annivasary" incorrect spelling of "anniversary"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">question form </t>
-  </si>
-  <si>
-    <t>Sentence ends with "yannada?"</t>
-  </si>
-  <si>
-    <t>english noun integration</t>
-  </si>
-  <si>
-    <t>"restaurant ekata"</t>
-  </si>
-  <si>
-    <t>Code-switching</t>
-  </si>
-  <si>
-    <t>Sinhala + English + abbreviations ("dnt wrry")</t>
-  </si>
-  <si>
-    <t>Full English slang in Singlish</t>
-  </si>
-  <si>
-    <t>"otw", "gonna b thr sn"</t>
-  </si>
-  <si>
-    <t>Technical term usage</t>
-  </si>
-  <si>
-    <t>"wifi signal" integrated with Sinhala</t>
-  </si>
-  <si>
-    <t>Command/request form</t>
-  </si>
-  <si>
-    <t>"send karannako"</t>
-  </si>
-  <si>
-    <t>Social media context</t>
-  </si>
-  <si>
-    <t>"Instagram eke post eka"</t>
-  </si>
-  <si>
-    <t>platform based sentence</t>
-  </si>
-  <si>
-    <t>"you tube eke video eka"</t>
-  </si>
-  <si>
-    <t>Acronyms usage</t>
-  </si>
-  <si>
-    <t>"ASAP" mixed with Sinhala</t>
-  </si>
-  <si>
-    <t>technical and sinhala mis</t>
-  </si>
-  <si>
-    <t>"NIC check karala"</t>
-  </si>
-  <si>
-    <t>Transport-related hybrid sentence</t>
-  </si>
-  <si>
-    <t>"bus eken", "uni eka"</t>
-  </si>
-  <si>
-    <t>Possessive Sinhala form</t>
-  </si>
-  <si>
-    <t>"oyalage lab eka"</t>
-  </si>
-  <si>
-    <t>Slang + abbreviation</t>
-  </si>
-  <si>
-    <t>"machan", "nxt wk"</t>
-  </si>
-  <si>
-    <t>Named entity + English</t>
-  </si>
-  <si>
-    <t>"dubai shopping"</t>
-  </si>
-  <si>
-    <t>Name entity + Sinhala suffix</t>
-  </si>
-  <si>
-    <t>"Kamal aiyee"</t>
-  </si>
-  <si>
-    <t>Person name + event context</t>
-  </si>
-  <si>
-    <t>"Thisara perera" in sports context</t>
-  </si>
-  <si>
-    <t>"50k" representing value</t>
-  </si>
-  <si>
-    <t>numeric shorthand</t>
-  </si>
-  <si>
-    <t>ordinal number usage</t>
-  </si>
-  <si>
-    <t>"2nd date"</t>
-  </si>
-  <si>
-    <t>Currency expression</t>
-  </si>
-  <si>
-    <t>"Rs. 3500"</t>
-  </si>
-  <si>
-    <t>Currency + question</t>
-  </si>
-  <si>
-    <t>"USD 500 kiyanne"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time expression </t>
-  </si>
-  <si>
-    <t>"8:30AM"</t>
-  </si>
-  <si>
-    <t>Time shorthand</t>
-  </si>
-  <si>
-    <t>"8am walata"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date expression </t>
-  </si>
-  <si>
-    <t>"March 22"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iso date format </t>
-  </si>
-  <si>
-    <t>"2026-04-30"</t>
-  </si>
-  <si>
-    <t>unit repetition error</t>
-  </si>
-  <si>
-    <t>"kg 12kg" incorrect duplication</t>
-  </si>
-  <si>
-    <t>Measurement expression</t>
-  </si>
-  <si>
-    <t>"km 5k"</t>
-  </si>
-  <si>
-    <t>Strong slang usage</t>
-  </si>
-  <si>
-    <t>"adoo", "elakiri", "bro"</t>
-  </si>
-  <si>
-    <t>"bng" for "bn" (ban/machan)</t>
-  </si>
-  <si>
-    <t>Mentions + hybrid sentence</t>
-  </si>
-  <si>
-    <t>"@saman" with Sinhala-English mix</t>
-  </si>
-  <si>
-    <t>Emoji + Singlish</t>
-  </si>
-  <si>
-    <t>"🎉" combined with greeting</t>
-  </si>
-  <si>
-    <t>Long paragraph + code-switching</t>
-  </si>
-  <si>
-    <t>Multi-sentence mix of Sinhala, English, and technical terms</t>
-  </si>
-  <si>
-    <t>L</t>
+    <t>Accuracy justification/ Description of issue type</t>
+  </si>
+  <si>
+    <t>What is covered by the test</t>
+  </si>
+  <si>
+    <t>Question forms</t>
+  </si>
+  <si>
+    <t>Rationale: The sentence "Oya monawada karanne?" is a direct question.</t>
+  </si>
+  <si>
+    <t>Rationale: The sentence "Uta enna kiyanne nadda?" is a question.</t>
+  </si>
+  <si>
+    <t>Command forms</t>
+  </si>
+  <si>
+    <t>Command forms; Requests</t>
+  </si>
+  <si>
+    <t>Rationale: The sentence conveys a command or instruction from "akka".</t>
+  </si>
+  <si>
+    <t>Rationale: "enna epa" is a command; "karunakarala" indicates a request.</t>
+  </si>
+  <si>
+    <t>Greetings</t>
+  </si>
+  <si>
+    <t>Rationale: "Jayen jayama wewa!" is a common Sinhala greeting/wish.</t>
+  </si>
+  <si>
+    <t>Rationale: "Ayubovan" is a formal greeting.</t>
+  </si>
+  <si>
+    <t>Requests</t>
+  </si>
+  <si>
+    <t>Rationale: "denawada?" with "Ane" acts as a polite request.</t>
+  </si>
+  <si>
+    <t>Rationale: Asking someone to deliver something ("deegena yanawada?").</t>
+  </si>
+  <si>
+    <t>Responses</t>
+  </si>
+  <si>
+    <t>Rationale: Providing a response to a previous context ("man liyala dannam").</t>
+  </si>
+  <si>
+    <t>Rationale: Direct negative response ("Na na").</t>
+  </si>
+  <si>
+    <t>Repeated Words</t>
+  </si>
+  <si>
+    <t>Evidence: Includes the repeated word "idala idala".</t>
+  </si>
+  <si>
+    <t>Evidence: Includes the repeated word "Epa epa".</t>
+  </si>
+  <si>
+    <t>Punctuation Marks</t>
+  </si>
+  <si>
+    <t>Rationale: Uses "..." and "?" within the sentence.</t>
+  </si>
+  <si>
+    <t>Rationale: Uses "!" and "?" to show emotion and questioning.</t>
+  </si>
+  <si>
+    <t>Romanization Variants</t>
+  </si>
+  <si>
+    <t>Rationale: Use of "siyee" instead of the standard "siya".</t>
+  </si>
+  <si>
+    <t>Rationale: "maddnam" and "Parkku" are non-standard spelling variants.</t>
+  </si>
+  <si>
+    <t>Isolated English Word</t>
+  </si>
+  <si>
+    <t>Evidence: The English word "office" is used in the Singlish sentence.</t>
+  </si>
+  <si>
+    <t>Evidence: The English word "phone" is used.</t>
+  </si>
+  <si>
+    <t>Multi-Word English Phrases</t>
+  </si>
+  <si>
+    <t>Evidence: Includes the phrase "See you tomorrow".</t>
+  </si>
+  <si>
+    <t>Evidence: Includes "dubai shopping" as a phrase.</t>
+  </si>
+  <si>
+    <t>English Digital Terms</t>
+  </si>
+  <si>
+    <t>Evidence: Includes the term "wifi signal".</t>
+  </si>
+  <si>
+    <t>Evidence: Includes the word "number".</t>
+  </si>
+  <si>
+    <t>Platform/App Names</t>
+  </si>
+  <si>
+    <t>Evidence: Mentions the service "Pick me".</t>
+  </si>
+  <si>
+    <t>Evidence: Mentions "facebook".</t>
+  </si>
+  <si>
+    <t>Abbreviations/Acronyms</t>
+  </si>
+  <si>
+    <t>Evidence: Uses the abbreviation "ID".</t>
+  </si>
+  <si>
+    <t>Evidence: Uses the technical abbreviation "EOD" (End of Day).</t>
+  </si>
+  <si>
+    <t>English Clipped Forms</t>
+  </si>
+  <si>
+    <t>Evidence: Uses "uni" as a clipped form for University.</t>
+  </si>
+  <si>
+    <t>Evidence: Uses "lab" as a clipped form for Laboratory.</t>
+  </si>
+  <si>
+    <t>Place Names Embedded</t>
+  </si>
+  <si>
+    <t>Evidence: Mentions the place "Kandy".</t>
+  </si>
+  <si>
+    <t>Evidence: Mentions the place "Riverston".</t>
+  </si>
+  <si>
+    <t>Person Names Embedded</t>
+  </si>
+  <si>
+    <t>Evidence: Mentions the person "Hashini".</t>
+  </si>
+  <si>
+    <t>Evidence: Mentions the person "Viweka".</t>
+  </si>
+  <si>
+    <t>Numbers and Suffixes</t>
+  </si>
+  <si>
+    <t>Evidence: Includes the alphanumeric code "ISO 4032".</t>
+  </si>
+  <si>
+    <t>Evidence: Includes the number "Grade 8".</t>
+  </si>
+  <si>
+    <t>Inputs with Currency</t>
+  </si>
+  <si>
+    <t>Evidence: Includes the currency format "Rs.3000".</t>
+  </si>
+  <si>
+    <t>Evidence: Includes the currency format "USD 50k".</t>
+  </si>
+  <si>
+    <t>Inputs with Time Formats</t>
+  </si>
+  <si>
+    <t>Evidence: Mentions the specific time "5am".</t>
+  </si>
+  <si>
+    <t>Evidence: Mentions the specific time "8am".</t>
+  </si>
+  <si>
+    <t>Inputs with Dates</t>
+  </si>
+  <si>
+    <t>Evidence: Includes the date "2026-6-10".</t>
+  </si>
+  <si>
+    <t>Evidence: Includes the date "March 25".</t>
+  </si>
+  <si>
+    <t>Unit of Measurements</t>
+  </si>
+  <si>
+    <t>Evidence: Uses "square feet" and "1200k".</t>
+  </si>
+  <si>
+    <t>Evidence: Uses the unit "2km".</t>
+  </si>
+  <si>
+    <t>Slang and Casual Phrasing</t>
+  </si>
+  <si>
+    <t>Evidence: Uses slang words "Adoh" and "cupiri".</t>
+  </si>
+  <si>
+    <t>Evidence: Uses the casual word "Patta" and "ban".</t>
+  </si>
+  <si>
+    <t>Online Identifiers</t>
+  </si>
+  <si>
+    <t>Evidence: Includes a URL "https:/www.youtube.com...".</t>
+  </si>
+  <si>
+    <t>Evidence: Includes an email address "anudi@gmail.com".</t>
+  </si>
+  <si>
+    <t>Inputs Containing Emojis</t>
+  </si>
+  <si>
+    <t>Evidence: Includes the emoji 😅.</t>
+  </si>
+  <si>
+    <t>Evidence: Includes the emoji 😔.</t>
+  </si>
+  <si>
+    <t>Rationale: Uses "genna" instead of "genenna".</t>
+  </si>
+  <si>
+    <t>Inputs with Currency, Romanization Variants</t>
+  </si>
+  <si>
+    <t>Evidence: Includes the currency format "Rs.3500".</t>
   </si>
 </sst>
 </file>
@@ -1052,24 +983,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1358,9 +1292,11 @@
     <col min="3" max="3" width="22.109375" customWidth="1"/>
     <col min="4" max="4" width="25.33203125" customWidth="1"/>
     <col min="5" max="5" width="22.5546875" customWidth="1"/>
-    <col min="7" max="7" width="36.5546875" customWidth="1"/>
-    <col min="8" max="8" width="31" customWidth="1"/>
-    <col min="9" max="10" width="12.33203125" customWidth="1"/>
+    <col min="7" max="7" width="34.33203125" customWidth="1"/>
+    <col min="8" max="8" width="39.21875" customWidth="1"/>
+    <col min="9" max="9" width="14.33203125" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="12" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1383,36 +1319,36 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>214</v>
+      <c r="F2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1446,29 +1382,29 @@
       <c r="H5" s="4"/>
     </row>
     <row r="6" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" s="7" t="s">
+      <c r="E6" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="H6" s="7" t="s">
-        <v>212</v>
+      <c r="H6" s="2" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1491,7 +1427,7 @@
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
-    <row r="9" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="56.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -1501,30 +1437,30 @@
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
     </row>
-    <row r="10" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
+    <row r="10" spans="1:8" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10" s="7" t="s">
+      <c r="F10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="H10" s="7" t="s">
-        <v>216</v>
+      <c r="H10" s="2" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1558,28 +1494,28 @@
       <c r="H13" s="4"/>
     </row>
     <row r="14" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="2" t="s">
+      <c r="E14" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="H14" s="7" t="s">
+      <c r="F14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>218</v>
       </c>
     </row>
@@ -1614,28 +1550,28 @@
       <c r="H17" s="4"/>
     </row>
     <row r="18" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" s="2" t="s">
+      <c r="E18" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G18" s="7" t="s">
+      <c r="F18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="H18" s="7" t="s">
+      <c r="H18" s="2" t="s">
         <v>220</v>
       </c>
     </row>
@@ -1670,29 +1606,29 @@
       <c r="H21" s="4"/>
     </row>
     <row r="22" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="E22" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G22" s="7" t="s">
+      <c r="F22" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="H22" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1726,29 +1662,29 @@
       <c r="H25" s="4"/>
     </row>
     <row r="26" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B26" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="2" t="s">
+      <c r="E26" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D26" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G26" s="7" t="s">
+      <c r="F26" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="H26" s="2" t="s">
         <v>223</v>
-      </c>
-      <c r="H26" s="7" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1782,29 +1718,29 @@
       <c r="H29" s="4"/>
     </row>
     <row r="30" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E30" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B30" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F30" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G30" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>226</v>
+      <c r="F30" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1838,29 +1774,29 @@
       <c r="H33" s="4"/>
     </row>
     <row r="34" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E34" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B34" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G34" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="H34" s="7" t="s">
-        <v>228</v>
+      <c r="F34" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1894,29 +1830,29 @@
       <c r="H37" s="4"/>
     </row>
     <row r="38" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="6" t="s">
+      <c r="A38" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E38" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B38" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G38" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="H38" s="7" t="s">
-        <v>230</v>
+      <c r="F38" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1950,29 +1886,29 @@
       <c r="H41" s="4"/>
     </row>
     <row r="42" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B42" s="7" t="s">
+      <c r="A42" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G42" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="H42" s="7" t="s">
-        <v>232</v>
+        <v>47</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2006,29 +1942,29 @@
       <c r="H45" s="4"/>
     </row>
     <row r="46" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B46" s="7" t="s">
+      <c r="A46" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="F46" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G46" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="H46" s="7" t="s">
-        <v>234</v>
+        <v>50</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2062,29 +1998,29 @@
       <c r="H49" s="4"/>
     </row>
     <row r="50" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B50" s="7" t="s">
+      <c r="A50" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E50" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G50" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="H50" s="7" t="s">
-        <v>236</v>
+        <v>54</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2118,29 +2054,29 @@
       <c r="H53" s="4"/>
     </row>
     <row r="54" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B54" s="7" t="s">
+      <c r="A54" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B54" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C54" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E54" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="D54" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="E54" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="F54" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G54" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="H54" s="7" t="s">
-        <v>238</v>
+      <c r="F54" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2174,29 +2110,29 @@
       <c r="H57" s="4"/>
     </row>
     <row r="58" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B58" s="7" t="s">
+      <c r="A58" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B58" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C58" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E58" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="D58" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E58" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F58" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G58" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="H58" s="7" t="s">
-        <v>240</v>
+      <c r="F58" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2230,29 +2166,29 @@
       <c r="H61" s="4"/>
     </row>
     <row r="62" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>7</v>
+      <c r="A62" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="C62" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E62" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="D62" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="E62" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="F62" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="G62" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="H62" s="7" t="s">
-        <v>242</v>
+      <c r="F62" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2286,29 +2222,29 @@
       <c r="H65" s="4"/>
     </row>
     <row r="66" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B66" s="7" t="s">
-        <v>13</v>
+      <c r="A66" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="C66" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E66" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="D66" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="E66" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="F66" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G66" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="H66" s="7" t="s">
-        <v>244</v>
+      <c r="F66" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2342,29 +2278,29 @@
       <c r="H69" s="4"/>
     </row>
     <row r="70" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="B70" s="7" t="s">
-        <v>7</v>
+      <c r="A70" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D70" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="E70" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="F70" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G70" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="H70" s="7" t="s">
-        <v>246</v>
+        <v>72</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E70" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2398,29 +2334,29 @@
       <c r="H73" s="4"/>
     </row>
     <row r="74" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="6" t="s">
+      <c r="A74" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E74" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="B74" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D74" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="E74" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="F74" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G74" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="H74" s="7" t="s">
-        <v>248</v>
+      <c r="F74" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2454,29 +2390,29 @@
       <c r="H77" s="4"/>
     </row>
     <row r="78" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="6" t="s">
+      <c r="A78" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E78" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="B78" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D78" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="E78" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="F78" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G78" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="H78" s="7" t="s">
-        <v>250</v>
+      <c r="F78" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2510,29 +2446,29 @@
       <c r="H81" s="4"/>
     </row>
     <row r="82" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="6" t="s">
+      <c r="A82" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E82" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B82" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D82" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="E82" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="F82" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G82" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="H82" s="7" t="s">
-        <v>252</v>
+      <c r="F82" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="83" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2566,29 +2502,29 @@
       <c r="H85" s="4"/>
     </row>
     <row r="86" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="B86" s="7" t="s">
-        <v>13</v>
+      <c r="A86" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D86" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="E86" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="F86" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G86" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="H86" s="7" t="s">
-        <v>254</v>
+        <v>87</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E86" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2622,29 +2558,29 @@
       <c r="H89" s="4"/>
     </row>
     <row r="90" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="B90" s="7" t="s">
-        <v>7</v>
+      <c r="A90" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D90" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="E90" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="F90" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G90" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="H90" s="7" t="s">
-        <v>256</v>
+        <v>91</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E90" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2678,29 +2614,29 @@
       <c r="H93" s="4"/>
     </row>
     <row r="94" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="B94" s="7" t="s">
-        <v>7</v>
+      <c r="A94" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D94" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="E94" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="F94" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G94" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="H94" s="7" t="s">
-        <v>258</v>
+        <v>95</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E94" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="95" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2734,29 +2670,29 @@
       <c r="H97" s="4"/>
     </row>
     <row r="98" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="B98" s="7" t="s">
-        <v>7</v>
+      <c r="A98" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D98" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="E98" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="F98" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G98" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="H98" s="7" t="s">
-        <v>260</v>
+        <v>99</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E98" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="99" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2790,29 +2726,29 @@
       <c r="H101" s="4"/>
     </row>
     <row r="102" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="B102" s="7" t="s">
+      <c r="A102" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B102" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D102" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="E102" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="F102" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G102" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="H102" s="7" t="s">
-        <v>262</v>
+        <v>102</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E102" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="103" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2846,29 +2782,29 @@
       <c r="H105" s="4"/>
     </row>
     <row r="106" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="B106" s="7" t="s">
+      <c r="A106" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B106" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="D106" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="E106" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="F106" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G106" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="H106" s="7" t="s">
-        <v>264</v>
+        <v>105</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E106" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="107" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2902,29 +2838,29 @@
       <c r="H109" s="4"/>
     </row>
     <row r="110" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="B110" s="7" t="s">
-        <v>13</v>
+      <c r="A110" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="D110" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="E110" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="F110" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G110" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="H110" s="7" t="s">
-        <v>266</v>
+        <v>190</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E110" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="111" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2958,29 +2894,29 @@
       <c r="H113" s="4"/>
     </row>
     <row r="114" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="B114" s="7" t="s">
-        <v>13</v>
+      <c r="A114" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D114" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="E114" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="F114" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G114" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="H114" s="7" t="s">
-        <v>268</v>
+        <v>110</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E114" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="115" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3014,29 +2950,29 @@
       <c r="H117" s="4"/>
     </row>
     <row r="118" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="B118" s="7" t="s">
-        <v>7</v>
+      <c r="A118" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>113</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D118" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="E118" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="F118" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G118" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="H118" s="7" t="s">
-        <v>270</v>
+        <v>114</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E118" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="F118" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G118" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="119" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3070,29 +3006,29 @@
       <c r="H121" s="4"/>
     </row>
     <row r="122" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="B122" s="7" t="s">
-        <v>7</v>
+      <c r="A122" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D122" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="E122" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="F122" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G122" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="H122" s="7" t="s">
-        <v>272</v>
+        <v>117</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E122" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="123" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3126,29 +3062,29 @@
       <c r="H125" s="4"/>
     </row>
     <row r="126" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="B126" s="7" t="s">
-        <v>13</v>
+      <c r="A126" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="D126" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="E126" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="F126" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G126" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="H126" s="7" t="s">
-        <v>274</v>
+        <v>120</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E126" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="127" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3182,29 +3118,29 @@
       <c r="H129" s="4"/>
     </row>
     <row r="130" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="B130" s="7" t="s">
+      <c r="A130" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B130" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D130" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="E130" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="F130" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G130" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="H130" s="7" t="s">
-        <v>276</v>
+        <v>124</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E130" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="F130" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G130" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="131" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3238,29 +3174,29 @@
       <c r="H133" s="4"/>
     </row>
     <row r="134" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="B134" s="7" t="s">
+      <c r="A134" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B134" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D134" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="E134" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="F134" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G134" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="H134" s="7" t="s">
-        <v>278</v>
+        <v>128</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E134" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G134" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="135" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3294,29 +3230,29 @@
       <c r="H137" s="4"/>
     </row>
     <row r="138" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="B138" s="7" t="s">
-        <v>7</v>
+      <c r="A138" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="D138" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="E138" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="F138" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G138" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="H138" s="7" t="s">
-        <v>280</v>
+        <v>132</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E138" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="F138" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G138" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="139" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3350,29 +3286,29 @@
       <c r="H141" s="4"/>
     </row>
     <row r="142" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="B142" s="7" t="s">
-        <v>7</v>
+      <c r="A142" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="D142" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="E142" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="F142" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G142" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="H142" s="7" t="s">
-        <v>281</v>
+        <v>136</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E142" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="F142" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G142" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="143" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3406,29 +3342,29 @@
       <c r="H145" s="4"/>
     </row>
     <row r="146" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="B146" s="7" t="s">
-        <v>13</v>
+      <c r="A146" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="D146" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="E146" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="F146" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G146" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="H146" s="7" t="s">
-        <v>284</v>
+        <v>140</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E146" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="F146" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G146" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="H146" s="2" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="147" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3462,29 +3398,29 @@
       <c r="H149" s="4"/>
     </row>
     <row r="150" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="B150" s="7" t="s">
+      <c r="A150" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="B150" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="D150" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="E150" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="F150" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G150" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="H150" s="7" t="s">
-        <v>286</v>
+        <v>144</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E150" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="F150" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G150" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="H150" s="2" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="151" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3518,29 +3454,29 @@
       <c r="H153" s="4"/>
     </row>
     <row r="154" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="B154" s="7" t="s">
-        <v>13</v>
+      <c r="A154" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="D154" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="E154" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="F154" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G154" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="H154" s="7" t="s">
-        <v>288</v>
+        <v>204</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="E154" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="F154" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G154" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="H154" s="2" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="155" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3574,29 +3510,29 @@
       <c r="H157" s="4"/>
     </row>
     <row r="158" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="B158" s="7" t="s">
+      <c r="A158" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B158" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="D158" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="E158" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="F158" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G158" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="H158" s="7" t="s">
-        <v>290</v>
+        <v>150</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E158" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="F158" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G158" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="H158" s="2" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="159" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3630,29 +3566,29 @@
       <c r="H161" s="4"/>
     </row>
     <row r="162" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="B162" s="7" t="s">
-        <v>7</v>
+      <c r="A162" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D162" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="E162" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="F162" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G162" s="7" t="s">
-        <v>291</v>
-      </c>
-      <c r="H162" s="7" t="s">
-        <v>292</v>
+        <v>153</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E162" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="F162" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G162" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="H162" s="2" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="163" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3686,29 +3622,29 @@
       <c r="H165" s="4"/>
     </row>
     <row r="166" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A166" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="B166" s="7" t="s">
-        <v>7</v>
+      <c r="A166" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="D166" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="E166" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="F166" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G166" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="H166" s="7" t="s">
-        <v>294</v>
+        <v>156</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E166" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="F166" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G166" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="H166" s="2" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="167" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3742,29 +3678,29 @@
       <c r="H169" s="4"/>
     </row>
     <row r="170" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="B170" s="7" t="s">
+      <c r="A170" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B170" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="D170" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="E170" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="F170" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G170" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="H170" s="7" t="s">
-        <v>296</v>
+        <v>160</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E170" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="F170" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G170" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="H170" s="2" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="171" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3798,29 +3734,29 @@
       <c r="H173" s="4"/>
     </row>
     <row r="174" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A174" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="B174" s="7" t="s">
+      <c r="A174" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="B174" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="D174" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="E174" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="F174" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G174" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="H174" s="7" t="s">
-        <v>298</v>
+        <v>164</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E174" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="F174" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G174" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="H174" s="2" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="175" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3854,29 +3790,29 @@
       <c r="H177" s="4"/>
     </row>
     <row r="178" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A178" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="B178" s="7" t="s">
-        <v>7</v>
+      <c r="A178" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="D178" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="E178" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="F178" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G178" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="H178" s="7" t="s">
-        <v>300</v>
+        <v>168</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E178" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="F178" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G178" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="H178" s="2" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="179" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3910,29 +3846,29 @@
       <c r="H181" s="4"/>
     </row>
     <row r="182" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A182" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="B182" s="7" t="s">
-        <v>7</v>
+      <c r="A182" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="D182" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="E182" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="F182" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G182" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="H182" s="7" t="s">
-        <v>302</v>
+        <v>172</v>
+      </c>
+      <c r="D182" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E182" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="F182" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G182" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="H182" s="2" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="183" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3966,29 +3902,29 @@
       <c r="H185" s="4"/>
     </row>
     <row r="186" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A186" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="B186" s="7" t="s">
+      <c r="A186" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="B186" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="D186" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="E186" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="F186" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G186" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="H186" s="7" t="s">
-        <v>303</v>
+        <v>176</v>
+      </c>
+      <c r="D186" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E186" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="F186" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G186" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="H186" s="2" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="187" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4022,29 +3958,29 @@
       <c r="H189" s="4"/>
     </row>
     <row r="190" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="B190" s="7" t="s">
-        <v>7</v>
+      <c r="A190" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="D190" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="E190" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="F190" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G190" s="7" t="s">
-        <v>304</v>
-      </c>
-      <c r="H190" s="7" t="s">
-        <v>305</v>
+        <v>180</v>
+      </c>
+      <c r="D190" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E190" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="F190" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G190" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="H190" s="2" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="191" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4078,27 +4014,29 @@
       <c r="H193" s="4"/>
     </row>
     <row r="194" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A194" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="B194" s="7" t="s">
-        <v>7</v>
+      <c r="A194" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="D194" s="5"/>
-      <c r="E194" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="F194" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="G194" s="7" t="s">
-        <v>306</v>
-      </c>
-      <c r="H194" s="7" t="s">
-        <v>307</v>
+        <v>184</v>
+      </c>
+      <c r="D194" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E194" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="F194" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G194" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="H194" s="2" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="195" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4132,29 +4070,29 @@
       <c r="H197" s="4"/>
     </row>
     <row r="198" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A198" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="B198" s="7" t="s">
-        <v>310</v>
+      <c r="A198" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="D198" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="E198" s="5" t="s">
+      <c r="D198" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="F198" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="G198" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="H198" s="7" t="s">
-        <v>309</v>
+      <c r="E198" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="F198" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G198" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="H198" s="2" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="199" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4189,154 +4127,334 @@
     </row>
   </sheetData>
   <mergeCells count="400">
+    <mergeCell ref="H178:H181"/>
+    <mergeCell ref="H182:H185"/>
+    <mergeCell ref="H186:H189"/>
+    <mergeCell ref="H190:H193"/>
+    <mergeCell ref="H194:H197"/>
+    <mergeCell ref="H198:H201"/>
+    <mergeCell ref="H142:H145"/>
+    <mergeCell ref="H146:H149"/>
+    <mergeCell ref="H150:H153"/>
+    <mergeCell ref="H154:H157"/>
+    <mergeCell ref="H158:H161"/>
+    <mergeCell ref="H162:H165"/>
+    <mergeCell ref="H166:H169"/>
+    <mergeCell ref="H170:H173"/>
+    <mergeCell ref="H174:H177"/>
+    <mergeCell ref="H106:H109"/>
+    <mergeCell ref="H110:H113"/>
+    <mergeCell ref="H114:H117"/>
+    <mergeCell ref="H118:H121"/>
+    <mergeCell ref="H122:H125"/>
+    <mergeCell ref="H126:H129"/>
+    <mergeCell ref="H130:H133"/>
+    <mergeCell ref="H134:H137"/>
+    <mergeCell ref="H138:H141"/>
+    <mergeCell ref="H70:H73"/>
+    <mergeCell ref="H74:H77"/>
+    <mergeCell ref="H78:H81"/>
+    <mergeCell ref="H82:H85"/>
+    <mergeCell ref="H86:H89"/>
+    <mergeCell ref="H90:H93"/>
+    <mergeCell ref="H94:H97"/>
+    <mergeCell ref="H98:H101"/>
+    <mergeCell ref="H102:H105"/>
+    <mergeCell ref="H34:H37"/>
+    <mergeCell ref="H38:H41"/>
+    <mergeCell ref="H42:H45"/>
+    <mergeCell ref="H46:H49"/>
+    <mergeCell ref="H50:H53"/>
+    <mergeCell ref="H54:H57"/>
+    <mergeCell ref="H58:H61"/>
+    <mergeCell ref="H62:H65"/>
+    <mergeCell ref="H66:H69"/>
+    <mergeCell ref="G178:G181"/>
     <mergeCell ref="G182:G185"/>
-    <mergeCell ref="H182:H185"/>
     <mergeCell ref="G186:G189"/>
-    <mergeCell ref="H186:H189"/>
     <mergeCell ref="G190:G193"/>
-    <mergeCell ref="H190:H193"/>
     <mergeCell ref="G194:G197"/>
-    <mergeCell ref="H194:H197"/>
     <mergeCell ref="G198:G201"/>
-    <mergeCell ref="H198:H201"/>
+    <mergeCell ref="G142:G145"/>
+    <mergeCell ref="G146:G149"/>
+    <mergeCell ref="G150:G153"/>
+    <mergeCell ref="G154:G157"/>
+    <mergeCell ref="G158:G161"/>
     <mergeCell ref="G162:G165"/>
-    <mergeCell ref="H162:H165"/>
     <mergeCell ref="G166:G169"/>
-    <mergeCell ref="H166:H169"/>
     <mergeCell ref="G170:G173"/>
-    <mergeCell ref="H170:H173"/>
     <mergeCell ref="G174:G177"/>
-    <mergeCell ref="H174:H177"/>
-    <mergeCell ref="G178:G181"/>
-    <mergeCell ref="H178:H181"/>
-    <mergeCell ref="G142:G145"/>
-    <mergeCell ref="H142:H145"/>
-    <mergeCell ref="G146:G149"/>
-    <mergeCell ref="H146:H149"/>
-    <mergeCell ref="G150:G153"/>
-    <mergeCell ref="H150:H153"/>
-    <mergeCell ref="G154:G157"/>
-    <mergeCell ref="H154:H157"/>
-    <mergeCell ref="G158:G161"/>
-    <mergeCell ref="H158:H161"/>
+    <mergeCell ref="G106:G109"/>
+    <mergeCell ref="G110:G113"/>
+    <mergeCell ref="G114:G117"/>
+    <mergeCell ref="G118:G121"/>
     <mergeCell ref="G122:G125"/>
-    <mergeCell ref="H122:H125"/>
     <mergeCell ref="G126:G129"/>
-    <mergeCell ref="H126:H129"/>
     <mergeCell ref="G130:G133"/>
-    <mergeCell ref="H130:H133"/>
     <mergeCell ref="G134:G137"/>
-    <mergeCell ref="H134:H137"/>
     <mergeCell ref="G138:G141"/>
-    <mergeCell ref="H138:H141"/>
+    <mergeCell ref="G70:G73"/>
+    <mergeCell ref="G74:G77"/>
+    <mergeCell ref="G78:G81"/>
+    <mergeCell ref="G82:G85"/>
+    <mergeCell ref="G86:G89"/>
+    <mergeCell ref="G90:G93"/>
+    <mergeCell ref="G94:G97"/>
+    <mergeCell ref="G98:G101"/>
     <mergeCell ref="G102:G105"/>
-    <mergeCell ref="H102:H105"/>
-    <mergeCell ref="G106:G109"/>
-    <mergeCell ref="H106:H109"/>
-    <mergeCell ref="G110:G113"/>
-    <mergeCell ref="H110:H113"/>
-    <mergeCell ref="G114:G117"/>
-    <mergeCell ref="H114:H117"/>
-    <mergeCell ref="G118:G121"/>
-    <mergeCell ref="H118:H121"/>
-    <mergeCell ref="G82:G85"/>
-    <mergeCell ref="H82:H85"/>
-    <mergeCell ref="G86:G89"/>
-    <mergeCell ref="H86:H89"/>
-    <mergeCell ref="G90:G93"/>
-    <mergeCell ref="H90:H93"/>
-    <mergeCell ref="G94:G97"/>
-    <mergeCell ref="H94:H97"/>
-    <mergeCell ref="G98:G101"/>
-    <mergeCell ref="H98:H101"/>
+    <mergeCell ref="G34:G37"/>
+    <mergeCell ref="G38:G41"/>
+    <mergeCell ref="G42:G45"/>
+    <mergeCell ref="G46:G49"/>
+    <mergeCell ref="G50:G53"/>
+    <mergeCell ref="G54:G57"/>
+    <mergeCell ref="G58:G61"/>
     <mergeCell ref="G62:G65"/>
-    <mergeCell ref="H62:H65"/>
     <mergeCell ref="G66:G69"/>
-    <mergeCell ref="H66:H69"/>
-    <mergeCell ref="G70:G73"/>
-    <mergeCell ref="H70:H73"/>
-    <mergeCell ref="G74:G77"/>
-    <mergeCell ref="H74:H77"/>
-    <mergeCell ref="G78:G81"/>
-    <mergeCell ref="H78:H81"/>
-    <mergeCell ref="H42:H45"/>
-    <mergeCell ref="G46:G49"/>
-    <mergeCell ref="H46:H49"/>
-    <mergeCell ref="G50:G53"/>
-    <mergeCell ref="H50:H53"/>
-    <mergeCell ref="G54:G57"/>
-    <mergeCell ref="H54:H57"/>
-    <mergeCell ref="G58:G61"/>
-    <mergeCell ref="H58:H61"/>
-    <mergeCell ref="C6:C9"/>
-    <mergeCell ref="C62:C65"/>
-    <mergeCell ref="A98:A101"/>
     <mergeCell ref="G2:G5"/>
     <mergeCell ref="H2:H5"/>
     <mergeCell ref="G6:G9"/>
+    <mergeCell ref="G10:G13"/>
+    <mergeCell ref="G14:G17"/>
+    <mergeCell ref="G18:G21"/>
+    <mergeCell ref="G22:G25"/>
+    <mergeCell ref="G26:G29"/>
+    <mergeCell ref="G30:G33"/>
     <mergeCell ref="H6:H9"/>
-    <mergeCell ref="G10:G13"/>
     <mergeCell ref="H10:H13"/>
-    <mergeCell ref="G14:G17"/>
     <mergeCell ref="H14:H17"/>
-    <mergeCell ref="G18:G21"/>
     <mergeCell ref="H18:H21"/>
-    <mergeCell ref="G22:G25"/>
     <mergeCell ref="H22:H25"/>
-    <mergeCell ref="G26:G29"/>
     <mergeCell ref="H26:H29"/>
-    <mergeCell ref="G30:G33"/>
     <mergeCell ref="H30:H33"/>
-    <mergeCell ref="G34:G37"/>
-    <mergeCell ref="H34:H37"/>
-    <mergeCell ref="G38:G41"/>
-    <mergeCell ref="H38:H41"/>
-    <mergeCell ref="G42:G45"/>
-    <mergeCell ref="A198:A201"/>
-    <mergeCell ref="F194:F197"/>
-    <mergeCell ref="C198:C201"/>
-    <mergeCell ref="D122:D125"/>
-    <mergeCell ref="C90:C93"/>
-    <mergeCell ref="F122:F125"/>
-    <mergeCell ref="D162:D165"/>
-    <mergeCell ref="C130:C133"/>
-    <mergeCell ref="A126:A129"/>
-    <mergeCell ref="C182:C185"/>
-    <mergeCell ref="E182:E185"/>
-    <mergeCell ref="C110:C113"/>
-    <mergeCell ref="F106:F109"/>
-    <mergeCell ref="A190:A193"/>
-    <mergeCell ref="F186:F189"/>
-    <mergeCell ref="C150:C153"/>
-    <mergeCell ref="C190:C193"/>
-    <mergeCell ref="B114:B117"/>
-    <mergeCell ref="D114:D117"/>
-    <mergeCell ref="B154:B157"/>
-    <mergeCell ref="C174:C177"/>
-    <mergeCell ref="F170:F173"/>
-    <mergeCell ref="B138:B141"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="B66:B69"/>
+    <mergeCell ref="C154:C157"/>
+    <mergeCell ref="C98:C101"/>
+    <mergeCell ref="E14:E17"/>
+    <mergeCell ref="A166:A169"/>
+    <mergeCell ref="E102:E105"/>
+    <mergeCell ref="B50:B53"/>
+    <mergeCell ref="A162:A165"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="D26:D29"/>
+    <mergeCell ref="A118:A121"/>
+    <mergeCell ref="E86:E89"/>
+    <mergeCell ref="B34:B37"/>
+    <mergeCell ref="F46:F49"/>
+    <mergeCell ref="E74:E77"/>
+    <mergeCell ref="F42:F45"/>
+    <mergeCell ref="B78:B81"/>
+    <mergeCell ref="D78:D81"/>
+    <mergeCell ref="D82:D85"/>
+    <mergeCell ref="C34:C37"/>
+    <mergeCell ref="C86:C89"/>
+    <mergeCell ref="F82:F85"/>
+    <mergeCell ref="D54:D57"/>
+    <mergeCell ref="C162:C165"/>
+    <mergeCell ref="B130:B133"/>
+    <mergeCell ref="C30:C33"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="A54:A57"/>
+    <mergeCell ref="D46:D49"/>
+    <mergeCell ref="C54:C57"/>
+    <mergeCell ref="A74:A77"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="B134:B137"/>
+    <mergeCell ref="A110:A113"/>
+    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="D198:D201"/>
+    <mergeCell ref="A90:A93"/>
+    <mergeCell ref="A146:A149"/>
+    <mergeCell ref="F198:F201"/>
+    <mergeCell ref="C146:C149"/>
+    <mergeCell ref="D174:D177"/>
+    <mergeCell ref="F174:F177"/>
+    <mergeCell ref="A178:A181"/>
+    <mergeCell ref="D126:D129"/>
+    <mergeCell ref="C94:C97"/>
+    <mergeCell ref="F126:F129"/>
+    <mergeCell ref="E94:E97"/>
+    <mergeCell ref="D166:D169"/>
+    <mergeCell ref="E90:E93"/>
+    <mergeCell ref="F110:F113"/>
+    <mergeCell ref="D150:D153"/>
+    <mergeCell ref="F150:F153"/>
+    <mergeCell ref="E158:E161"/>
+    <mergeCell ref="B166:B169"/>
+    <mergeCell ref="B118:B121"/>
+    <mergeCell ref="E110:E113"/>
+    <mergeCell ref="F94:F97"/>
+    <mergeCell ref="F98:F101"/>
+    <mergeCell ref="E130:E133"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="B158:B161"/>
+    <mergeCell ref="E154:E157"/>
+    <mergeCell ref="C2:C5"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="E2:E5"/>
+    <mergeCell ref="C82:C85"/>
+    <mergeCell ref="B186:B189"/>
+    <mergeCell ref="D102:D105"/>
+    <mergeCell ref="B142:B145"/>
+    <mergeCell ref="E174:E177"/>
+    <mergeCell ref="D142:D145"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A150:A153"/>
+    <mergeCell ref="E26:E29"/>
+    <mergeCell ref="D98:D101"/>
+    <mergeCell ref="C66:C69"/>
+    <mergeCell ref="E66:E69"/>
+    <mergeCell ref="A102:A105"/>
+    <mergeCell ref="C102:C105"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="E50:E53"/>
+    <mergeCell ref="B194:B197"/>
+    <mergeCell ref="D10:D13"/>
+    <mergeCell ref="B90:B93"/>
+    <mergeCell ref="D50:D53"/>
+    <mergeCell ref="F10:F13"/>
+    <mergeCell ref="A94:A97"/>
+    <mergeCell ref="F146:F149"/>
+    <mergeCell ref="B122:B125"/>
+    <mergeCell ref="E150:E153"/>
+    <mergeCell ref="D178:D181"/>
+    <mergeCell ref="D34:D37"/>
+    <mergeCell ref="F178:F181"/>
+    <mergeCell ref="C42:C45"/>
+    <mergeCell ref="F34:F37"/>
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="F74:F77"/>
+    <mergeCell ref="E42:E45"/>
+    <mergeCell ref="A78:A81"/>
+    <mergeCell ref="A182:A185"/>
+    <mergeCell ref="B106:B109"/>
+    <mergeCell ref="E186:E189"/>
+    <mergeCell ref="C106:C109"/>
+    <mergeCell ref="A194:A197"/>
+    <mergeCell ref="C46:C49"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="D2:D5"/>
+    <mergeCell ref="B42:B45"/>
+    <mergeCell ref="C22:C25"/>
+    <mergeCell ref="F18:F21"/>
+    <mergeCell ref="E122:E125"/>
+    <mergeCell ref="E78:E81"/>
+    <mergeCell ref="B170:B173"/>
+    <mergeCell ref="A174:A177"/>
+    <mergeCell ref="D170:D173"/>
+    <mergeCell ref="B58:B61"/>
+    <mergeCell ref="F2:F5"/>
+    <mergeCell ref="E6:E9"/>
+    <mergeCell ref="C134:C137"/>
+    <mergeCell ref="F22:F25"/>
+    <mergeCell ref="A154:A157"/>
+    <mergeCell ref="C114:C117"/>
+    <mergeCell ref="E30:E33"/>
+    <mergeCell ref="E114:E117"/>
+    <mergeCell ref="E170:E173"/>
+    <mergeCell ref="A46:A49"/>
+    <mergeCell ref="C70:C73"/>
+    <mergeCell ref="F102:F105"/>
+    <mergeCell ref="E70:E73"/>
+    <mergeCell ref="F190:F193"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="C138:C141"/>
+    <mergeCell ref="C178:C181"/>
+    <mergeCell ref="E54:E57"/>
+    <mergeCell ref="D30:D33"/>
+    <mergeCell ref="E178:E181"/>
+    <mergeCell ref="D62:D65"/>
+    <mergeCell ref="D118:D121"/>
+    <mergeCell ref="F62:F65"/>
+    <mergeCell ref="E126:E129"/>
+    <mergeCell ref="C166:C169"/>
+    <mergeCell ref="C58:C61"/>
+    <mergeCell ref="E58:E61"/>
+    <mergeCell ref="D90:D93"/>
+    <mergeCell ref="B46:B49"/>
+    <mergeCell ref="B102:B105"/>
+    <mergeCell ref="E138:E141"/>
+    <mergeCell ref="E190:E193"/>
+    <mergeCell ref="D158:D161"/>
+    <mergeCell ref="B98:B101"/>
+    <mergeCell ref="F114:F117"/>
+    <mergeCell ref="D154:D157"/>
+    <mergeCell ref="B178:B181"/>
+    <mergeCell ref="B198:B201"/>
+    <mergeCell ref="D14:D17"/>
+    <mergeCell ref="A106:A109"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="B174:B177"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="B126:B129"/>
+    <mergeCell ref="D182:D185"/>
+    <mergeCell ref="D38:D41"/>
+    <mergeCell ref="F182:F185"/>
+    <mergeCell ref="A130:A133"/>
+    <mergeCell ref="A82:A85"/>
+    <mergeCell ref="B110:B113"/>
+    <mergeCell ref="E106:E109"/>
+    <mergeCell ref="D110:D113"/>
+    <mergeCell ref="B54:B57"/>
+    <mergeCell ref="E146:E149"/>
+    <mergeCell ref="A58:A61"/>
+    <mergeCell ref="F166:F169"/>
+    <mergeCell ref="E198:E201"/>
+    <mergeCell ref="C74:C77"/>
+    <mergeCell ref="C126:C129"/>
+    <mergeCell ref="F162:F165"/>
+    <mergeCell ref="B94:B97"/>
+    <mergeCell ref="C118:C121"/>
+    <mergeCell ref="A158:A161"/>
+    <mergeCell ref="D186:D189"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="C50:C53"/>
+    <mergeCell ref="B82:B85"/>
+    <mergeCell ref="A86:A89"/>
+    <mergeCell ref="F138:F141"/>
+    <mergeCell ref="C142:C145"/>
+    <mergeCell ref="F90:F93"/>
+    <mergeCell ref="E118:E121"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="E46:E49"/>
+    <mergeCell ref="D66:D69"/>
+    <mergeCell ref="D106:D109"/>
+    <mergeCell ref="F66:F69"/>
+    <mergeCell ref="B146:B149"/>
+    <mergeCell ref="D18:D21"/>
+    <mergeCell ref="D146:D149"/>
+    <mergeCell ref="E166:E169"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="F30:F33"/>
+    <mergeCell ref="E38:E41"/>
+    <mergeCell ref="F158:F161"/>
+    <mergeCell ref="B190:B193"/>
+    <mergeCell ref="D194:D197"/>
+    <mergeCell ref="F38:F41"/>
+    <mergeCell ref="F50:F53"/>
+    <mergeCell ref="B74:B77"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="E162:E165"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="D130:D133"/>
+    <mergeCell ref="F130:F133"/>
+    <mergeCell ref="B162:B165"/>
+    <mergeCell ref="A134:A137"/>
+    <mergeCell ref="C18:C21"/>
+    <mergeCell ref="E18:E21"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="D22:D25"/>
+    <mergeCell ref="D74:D77"/>
     <mergeCell ref="E134:E137"/>
-    <mergeCell ref="D6:D9"/>
-    <mergeCell ref="C26:C29"/>
-    <mergeCell ref="D190:D193"/>
-    <mergeCell ref="B86:B89"/>
-    <mergeCell ref="A138:A141"/>
-    <mergeCell ref="E82:E85"/>
-    <mergeCell ref="D86:D89"/>
-    <mergeCell ref="F6:F9"/>
-    <mergeCell ref="F86:F89"/>
-    <mergeCell ref="F142:F145"/>
-    <mergeCell ref="C10:C13"/>
-    <mergeCell ref="B62:B65"/>
-    <mergeCell ref="E10:E13"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="B70:B73"/>
-    <mergeCell ref="D70:D73"/>
-    <mergeCell ref="E98:E101"/>
-    <mergeCell ref="F70:F73"/>
-    <mergeCell ref="E34:E37"/>
-    <mergeCell ref="B182:B185"/>
-    <mergeCell ref="D134:D137"/>
+    <mergeCell ref="D138:D141"/>
+    <mergeCell ref="F54:F57"/>
+    <mergeCell ref="C158:C161"/>
+    <mergeCell ref="F26:F29"/>
+    <mergeCell ref="F154:F157"/>
     <mergeCell ref="F134:F137"/>
     <mergeCell ref="E62:E65"/>
     <mergeCell ref="E22:E25"/>
@@ -4358,237 +4476,57 @@
     <mergeCell ref="A114:A117"/>
     <mergeCell ref="A170:A173"/>
     <mergeCell ref="A70:A73"/>
+    <mergeCell ref="F78:F81"/>
     <mergeCell ref="C170:C173"/>
-    <mergeCell ref="F78:F81"/>
     <mergeCell ref="F118:F121"/>
-    <mergeCell ref="F158:F161"/>
-    <mergeCell ref="B190:B193"/>
-    <mergeCell ref="D194:D197"/>
-    <mergeCell ref="F54:F57"/>
+    <mergeCell ref="C174:C177"/>
+    <mergeCell ref="F170:F173"/>
+    <mergeCell ref="B138:B141"/>
+    <mergeCell ref="D6:D9"/>
+    <mergeCell ref="C26:C29"/>
+    <mergeCell ref="D190:D193"/>
+    <mergeCell ref="B86:B89"/>
+    <mergeCell ref="E82:E85"/>
+    <mergeCell ref="A138:A141"/>
+    <mergeCell ref="D86:D89"/>
+    <mergeCell ref="F6:F9"/>
+    <mergeCell ref="F86:F89"/>
+    <mergeCell ref="F142:F145"/>
+    <mergeCell ref="C10:C13"/>
+    <mergeCell ref="B62:B65"/>
+    <mergeCell ref="E10:E13"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="B70:B73"/>
+    <mergeCell ref="D70:D73"/>
+    <mergeCell ref="E98:E101"/>
+    <mergeCell ref="F70:F73"/>
+    <mergeCell ref="E34:E37"/>
+    <mergeCell ref="B182:B185"/>
+    <mergeCell ref="D134:D137"/>
+    <mergeCell ref="C6:C9"/>
+    <mergeCell ref="C62:C65"/>
+    <mergeCell ref="A98:A101"/>
+    <mergeCell ref="A198:A201"/>
+    <mergeCell ref="F194:F197"/>
+    <mergeCell ref="C198:C201"/>
+    <mergeCell ref="D122:D125"/>
+    <mergeCell ref="C90:C93"/>
+    <mergeCell ref="F122:F125"/>
+    <mergeCell ref="D162:D165"/>
+    <mergeCell ref="C130:C133"/>
+    <mergeCell ref="A126:A129"/>
+    <mergeCell ref="C182:C185"/>
     <mergeCell ref="A142:A145"/>
-    <mergeCell ref="F26:F29"/>
-    <mergeCell ref="C118:C121"/>
-    <mergeCell ref="F154:F157"/>
-    <mergeCell ref="A158:A161"/>
-    <mergeCell ref="C30:C33"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="A54:A57"/>
-    <mergeCell ref="D186:D189"/>
-    <mergeCell ref="A50:A53"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="C50:C53"/>
-    <mergeCell ref="B82:B85"/>
-    <mergeCell ref="A86:A89"/>
-    <mergeCell ref="F138:F141"/>
-    <mergeCell ref="C142:C145"/>
-    <mergeCell ref="F90:F93"/>
-    <mergeCell ref="E118:E121"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="E46:E49"/>
-    <mergeCell ref="C158:C161"/>
-    <mergeCell ref="D66:D69"/>
-    <mergeCell ref="D106:D109"/>
-    <mergeCell ref="B146:B149"/>
-    <mergeCell ref="F66:F69"/>
-    <mergeCell ref="D18:D21"/>
-    <mergeCell ref="D146:D149"/>
-    <mergeCell ref="E166:E169"/>
-    <mergeCell ref="F30:F33"/>
-    <mergeCell ref="C162:C165"/>
-    <mergeCell ref="B130:B133"/>
-    <mergeCell ref="E38:E41"/>
-    <mergeCell ref="B198:B201"/>
-    <mergeCell ref="A106:A109"/>
-    <mergeCell ref="D14:D17"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="B174:B177"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="B126:B129"/>
-    <mergeCell ref="D182:D185"/>
-    <mergeCell ref="A130:A133"/>
-    <mergeCell ref="F182:F185"/>
-    <mergeCell ref="D38:D41"/>
-    <mergeCell ref="A82:A85"/>
-    <mergeCell ref="B110:B113"/>
-    <mergeCell ref="E106:E109"/>
-    <mergeCell ref="D110:D113"/>
-    <mergeCell ref="B54:B57"/>
-    <mergeCell ref="E146:E149"/>
-    <mergeCell ref="A58:A61"/>
-    <mergeCell ref="F166:F169"/>
-    <mergeCell ref="E198:E201"/>
-    <mergeCell ref="C74:C77"/>
-    <mergeCell ref="B94:B97"/>
-    <mergeCell ref="C126:C129"/>
-    <mergeCell ref="F162:F165"/>
-    <mergeCell ref="F190:F193"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="C138:C141"/>
-    <mergeCell ref="C178:C181"/>
-    <mergeCell ref="E54:E57"/>
-    <mergeCell ref="D30:D33"/>
-    <mergeCell ref="E178:E181"/>
-    <mergeCell ref="D62:D65"/>
-    <mergeCell ref="D118:D121"/>
-    <mergeCell ref="F62:F65"/>
-    <mergeCell ref="E126:E129"/>
-    <mergeCell ref="C166:C169"/>
-    <mergeCell ref="C58:C61"/>
-    <mergeCell ref="E58:E61"/>
-    <mergeCell ref="D90:D93"/>
-    <mergeCell ref="B46:B49"/>
-    <mergeCell ref="B102:B105"/>
-    <mergeCell ref="E138:E141"/>
-    <mergeCell ref="D158:D161"/>
-    <mergeCell ref="E190:E193"/>
-    <mergeCell ref="B98:B101"/>
-    <mergeCell ref="F114:F117"/>
-    <mergeCell ref="D154:D157"/>
-    <mergeCell ref="B178:B181"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="D2:D5"/>
-    <mergeCell ref="B42:B45"/>
-    <mergeCell ref="C22:C25"/>
-    <mergeCell ref="E122:E125"/>
-    <mergeCell ref="F18:F21"/>
-    <mergeCell ref="B170:B173"/>
-    <mergeCell ref="E78:E81"/>
-    <mergeCell ref="A174:A177"/>
-    <mergeCell ref="D170:D173"/>
-    <mergeCell ref="B58:B61"/>
-    <mergeCell ref="F2:F5"/>
-    <mergeCell ref="E6:E9"/>
-    <mergeCell ref="C134:C137"/>
-    <mergeCell ref="F22:F25"/>
-    <mergeCell ref="C114:C117"/>
-    <mergeCell ref="A154:A157"/>
-    <mergeCell ref="E30:E33"/>
-    <mergeCell ref="E170:E173"/>
-    <mergeCell ref="A46:A49"/>
-    <mergeCell ref="E114:E117"/>
-    <mergeCell ref="F102:F105"/>
-    <mergeCell ref="C46:C49"/>
-    <mergeCell ref="C70:C73"/>
-    <mergeCell ref="B194:B197"/>
-    <mergeCell ref="D10:D13"/>
-    <mergeCell ref="B90:B93"/>
-    <mergeCell ref="D50:D53"/>
-    <mergeCell ref="F10:F13"/>
-    <mergeCell ref="A94:A97"/>
-    <mergeCell ref="F146:F149"/>
-    <mergeCell ref="B122:B125"/>
-    <mergeCell ref="E150:E153"/>
-    <mergeCell ref="D178:D181"/>
-    <mergeCell ref="D34:D37"/>
-    <mergeCell ref="A182:A185"/>
-    <mergeCell ref="C42:C45"/>
-    <mergeCell ref="F34:F37"/>
-    <mergeCell ref="B18:B21"/>
-    <mergeCell ref="F74:F77"/>
-    <mergeCell ref="A78:A81"/>
-    <mergeCell ref="E42:E45"/>
-    <mergeCell ref="F178:F181"/>
-    <mergeCell ref="B106:B109"/>
-    <mergeCell ref="E186:E189"/>
-    <mergeCell ref="A194:A197"/>
-    <mergeCell ref="E70:E73"/>
-    <mergeCell ref="C106:C109"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="B158:B161"/>
-    <mergeCell ref="D78:D81"/>
-    <mergeCell ref="C2:C5"/>
-    <mergeCell ref="B6:B9"/>
-    <mergeCell ref="E2:E5"/>
-    <mergeCell ref="B186:B189"/>
-    <mergeCell ref="C82:C85"/>
-    <mergeCell ref="D102:D105"/>
-    <mergeCell ref="B142:B145"/>
-    <mergeCell ref="E174:E177"/>
-    <mergeCell ref="D142:D145"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A150:A153"/>
-    <mergeCell ref="E26:E29"/>
-    <mergeCell ref="D98:D101"/>
-    <mergeCell ref="C66:C69"/>
-    <mergeCell ref="A102:A105"/>
-    <mergeCell ref="E66:E69"/>
-    <mergeCell ref="C102:C105"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="B26:B29"/>
-    <mergeCell ref="D26:D29"/>
-    <mergeCell ref="D198:D201"/>
-    <mergeCell ref="A90:A93"/>
-    <mergeCell ref="A146:A149"/>
-    <mergeCell ref="F198:F201"/>
-    <mergeCell ref="C146:C149"/>
-    <mergeCell ref="D174:D177"/>
-    <mergeCell ref="A178:A181"/>
-    <mergeCell ref="F174:F177"/>
-    <mergeCell ref="D126:D129"/>
-    <mergeCell ref="C94:C97"/>
-    <mergeCell ref="F126:F129"/>
-    <mergeCell ref="D166:D169"/>
-    <mergeCell ref="E94:E97"/>
-    <mergeCell ref="E90:E93"/>
-    <mergeCell ref="F110:F113"/>
-    <mergeCell ref="D150:D153"/>
-    <mergeCell ref="F150:F153"/>
-    <mergeCell ref="E158:E161"/>
-    <mergeCell ref="B166:B169"/>
-    <mergeCell ref="B118:B121"/>
-    <mergeCell ref="E154:E157"/>
-    <mergeCell ref="E110:E113"/>
-    <mergeCell ref="F94:F97"/>
-    <mergeCell ref="F98:F101"/>
-    <mergeCell ref="F82:F85"/>
-    <mergeCell ref="E130:E133"/>
-    <mergeCell ref="D54:D57"/>
-    <mergeCell ref="B134:B137"/>
-    <mergeCell ref="A110:A113"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="B66:B69"/>
-    <mergeCell ref="D46:D49"/>
-    <mergeCell ref="C54:C57"/>
-    <mergeCell ref="A74:A77"/>
-    <mergeCell ref="B38:B41"/>
-    <mergeCell ref="F46:F49"/>
-    <mergeCell ref="E74:E77"/>
-    <mergeCell ref="B78:B81"/>
-    <mergeCell ref="F42:F45"/>
-    <mergeCell ref="E50:E53"/>
-    <mergeCell ref="F38:F41"/>
-    <mergeCell ref="B74:B77"/>
-    <mergeCell ref="F50:F53"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="D130:D133"/>
-    <mergeCell ref="F130:F133"/>
-    <mergeCell ref="A134:A137"/>
-    <mergeCell ref="C18:C21"/>
-    <mergeCell ref="C154:C157"/>
-    <mergeCell ref="C98:C101"/>
-    <mergeCell ref="E14:E17"/>
-    <mergeCell ref="A166:A169"/>
-    <mergeCell ref="E102:E105"/>
-    <mergeCell ref="B50:B53"/>
-    <mergeCell ref="A162:A165"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="A66:A69"/>
-    <mergeCell ref="A118:A121"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="E86:E89"/>
-    <mergeCell ref="B34:B37"/>
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="D82:D85"/>
-    <mergeCell ref="C34:C37"/>
-    <mergeCell ref="C86:C89"/>
-    <mergeCell ref="E162:E165"/>
-    <mergeCell ref="B162:B165"/>
-    <mergeCell ref="B22:B25"/>
-    <mergeCell ref="E18:E21"/>
-    <mergeCell ref="D22:D25"/>
-    <mergeCell ref="D74:D77"/>
-    <mergeCell ref="D138:D141"/>
+    <mergeCell ref="E182:E185"/>
+    <mergeCell ref="C110:C113"/>
+    <mergeCell ref="F106:F109"/>
+    <mergeCell ref="A190:A193"/>
+    <mergeCell ref="C150:C153"/>
+    <mergeCell ref="F186:F189"/>
+    <mergeCell ref="C190:C193"/>
+    <mergeCell ref="B114:B117"/>
+    <mergeCell ref="D114:D117"/>
+    <mergeCell ref="B154:B157"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
